--- a/src/attributions/attributions_saliency_traj_263.xlsx
+++ b/src/attributions/attributions_saliency_traj_263.xlsx
@@ -1568,3985 +1568,3985 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0913347452878952</v>
+        <v>0.001187743851915002</v>
       </c>
       <c r="B3" t="n">
-        <v>1.209086537361145</v>
+        <v>0.1697713136672974</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01896288990974426</v>
+        <v>0.05967961996793747</v>
       </c>
       <c r="D3" t="n">
-        <v>0.391652911901474</v>
+        <v>0.02855911105871201</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2143160402774811</v>
+        <v>0.01595369353890419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9807802438735962</v>
+        <v>0.1072946637868881</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1791854649782181</v>
+        <v>0.01544007658958435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1271970719099045</v>
+        <v>0.008936057798564434</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1453084796667099</v>
+        <v>0.001992870587855577</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03551727905869484</v>
+        <v>0.02777419798076153</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9337085485458374</v>
+        <v>0.1861443370580673</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04982095584273338</v>
+        <v>0.06065851822495461</v>
       </c>
       <c r="M3" t="n">
-        <v>0.26805180311203</v>
+        <v>0.06997963786125183</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2300635576248169</v>
+        <v>0.04580604657530785</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5752420425415039</v>
+        <v>0.09675735980272293</v>
       </c>
       <c r="P3" t="n">
-        <v>0.09419393539428711</v>
+        <v>0.01081205159425735</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2064135074615479</v>
+        <v>0.04005955159664154</v>
       </c>
       <c r="R3" t="n">
-        <v>0.05459420755505562</v>
+        <v>0.006926394999027252</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1632939428091049</v>
+        <v>0.0010766526684165</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1344155669212341</v>
+        <v>0.04031144082546234</v>
       </c>
       <c r="U3" t="n">
-        <v>0.05825851112604141</v>
+        <v>0.01557656563818455</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3342463374137878</v>
+        <v>0.0324241891503334</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3000189661979675</v>
+        <v>0.001476619159802794</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05323636531829834</v>
+        <v>0.01445897109806538</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004696767777204514</v>
+        <v>0.001993425888940692</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.08619685471057892</v>
+        <v>0.01729187183082104</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03345439583063126</v>
+        <v>0.00598627608269453</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004205048084259033</v>
+        <v>0.01228960603475571</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.01001317799091339</v>
+        <v>0.04406977817416191</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1558966636657715</v>
+        <v>0.01845197007060051</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.03495825454592705</v>
+        <v>0.0364491306245327</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.07433885335922241</v>
+        <v>0.02401139959692955</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.008212728425860405</v>
+        <v>0.03058125451207161</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2302647083997726</v>
+        <v>0.01089293882250786</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.2834267616271973</v>
+        <v>0.06236259266734123</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01208964735269547</v>
+        <v>0.004097863100469112</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.2965582013130188</v>
+        <v>0.00399500411003828</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.001211110502481461</v>
+        <v>0.04406389966607094</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.05195203796029091</v>
+        <v>0.02687813527882099</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.1234007775783539</v>
+        <v>0.01915228366851807</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.03643295168876648</v>
+        <v>0.05199988558888435</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.19002665579319</v>
+        <v>0.0194675400853157</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001874838024377823</v>
+        <v>0.01716655679047108</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.07347775995731354</v>
+        <v>0.05204116553068161</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.09665779024362564</v>
+        <v>0.007265618070960045</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.2016604542732239</v>
+        <v>0.008888794109225273</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.6191573739051819</v>
+        <v>0.2169045060873032</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.00351807102560997</v>
+        <v>0.002563199028372765</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1270191073417664</v>
+        <v>0.02913101017475128</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.6294209361076355</v>
+        <v>0.02815900184214115</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.7363102436065674</v>
+        <v>0.05440215766429901</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.323906272649765</v>
+        <v>0.007398928515613079</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.2084606885910034</v>
+        <v>0.01670657284557819</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.2524559497833252</v>
+        <v>0.02038556896150112</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.04315101355314255</v>
+        <v>0.01528389845043421</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.06480260193347931</v>
+        <v>0.08720766752958298</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.003445830196142197</v>
+        <v>0.03509726002812386</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1240452080965042</v>
+        <v>0.005480404477566481</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.05567176640033722</v>
+        <v>0.0715729147195816</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.06590371578931808</v>
+        <v>0.001799465506337583</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.03532072156667709</v>
+        <v>0.01955192722380161</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.007259966805577278</v>
+        <v>0.05011948198080063</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.05018050968647003</v>
+        <v>0.009286032058298588</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.07526159286499023</v>
+        <v>0.01498986594378948</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.2089007496833801</v>
+        <v>0.003871255088597536</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1807483434677124</v>
+        <v>0.02792686969041824</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.1513190269470215</v>
+        <v>0.01646754145622253</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.04667267948389053</v>
+        <v>0.002979319542646408</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.07886222004890442</v>
+        <v>0.02208423614501953</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1116575747728348</v>
+        <v>0.04902933165431023</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.2566925287246704</v>
+        <v>0.008941108360886574</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.3022110164165497</v>
+        <v>0.01007650606334209</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.002071671187877655</v>
+        <v>0.006748845335096121</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.4681968688964844</v>
+        <v>0.1612178385257721</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0232388898730278</v>
+        <v>0.002685411600396037</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1789876073598862</v>
+        <v>0.04116801172494888</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1990698426961899</v>
+        <v>0.01245508994907141</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.2572070062160492</v>
+        <v>0.05209939554333687</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.001116983592510223</v>
+        <v>0.01293499767780304</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.03413379937410355</v>
+        <v>0.008691792376339436</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.001179004088044167</v>
+        <v>0.001417280174791813</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.01072315126657486</v>
+        <v>0.0008784726960584521</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1797238290309906</v>
+        <v>0.06268712878227234</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.006150906905531883</v>
+        <v>0.0247499868273735</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.01103382743895054</v>
+        <v>0.00194963370449841</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.02981962077319622</v>
+        <v>0.002409185748547316</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1919058710336685</v>
+        <v>0.02062786743044853</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.02024774253368378</v>
+        <v>0.009816845878958702</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1118122786283493</v>
+        <v>0.01080845575779676</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.01303605828434229</v>
+        <v>0.007180728949606419</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.2089603245258331</v>
+        <v>0.01422279421240091</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1703452914953232</v>
+        <v>0.06814390420913696</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0345698744058609</v>
+        <v>0.01673212088644505</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.09070014953613281</v>
+        <v>0.04457342252135277</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1780749410390854</v>
+        <v>0.05296707898378372</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.2804883718490601</v>
+        <v>0.01239454746246338</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.06812599301338196</v>
+        <v>0.03192966431379318</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.05372050777077675</v>
+        <v>0.03246664628386497</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.02588595449924469</v>
+        <v>0.007190187461674213</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.02890949323773384</v>
+        <v>0.01168435160070658</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1978724598884583</v>
+        <v>0.06041223555803299</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.02109602652490139</v>
+        <v>0.02806057408452034</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0349908247590065</v>
+        <v>0.004394402261823416</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01127855852246284</v>
+        <v>0.005123899783939123</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.200862854719162</v>
+        <v>0.02450919337570667</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.02182914316654205</v>
+        <v>0.001733449287712574</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.2322530597448349</v>
+        <v>0.006549150682985783</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.01381035894155502</v>
+        <v>0.0045971954241395</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.004022329580038786</v>
+        <v>0.02963361889123917</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.5400466918945312</v>
+        <v>0.04631447046995163</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.08469115197658539</v>
+        <v>0.01158900652080774</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.2370386570692062</v>
+        <v>0.03565287590026855</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.637444794178009</v>
+        <v>0.02396747097373009</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.01689973846077919</v>
+        <v>0.03989151492714882</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.07389795780181885</v>
+        <v>0.01425992883741856</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.3204131722450256</v>
+        <v>0.02562437951564789</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.3005699515342712</v>
+        <v>0.03241143375635147</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.1560772210359573</v>
+        <v>0.0107239093631506</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.110918827354908</v>
+        <v>0.02369281277060509</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.003019455820322037</v>
+        <v>0.00957522913813591</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.006817951798439026</v>
+        <v>0.03993624821305275</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.07273642718791962</v>
+        <v>0.004537822213023901</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.07997315376996994</v>
+        <v>0.03213528171181679</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.05157133936882019</v>
+        <v>0.002475128043442965</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.004517602734267712</v>
+        <v>0.006085497792810202</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.02992358803749084</v>
+        <v>0.01004083268344402</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.03241794928908348</v>
+        <v>0.01267107576131821</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.02246711775660515</v>
+        <v>0.02813426032662392</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.05032297596335411</v>
+        <v>0.02746688574552536</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.03691073879599571</v>
+        <v>0.003942197188735008</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.1162273287773132</v>
+        <v>0.009829584509134293</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.1625016629695892</v>
+        <v>0.01192782912403345</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.06149062514305115</v>
+        <v>0.001579017378389835</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.2246359437704086</v>
+        <v>0.006994898896664381</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.2134931981563568</v>
+        <v>0.0364823155105114</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.1928914338350296</v>
+        <v>0.004504716955125332</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.1388669908046722</v>
+        <v>0.03228418901562691</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.05079872161149979</v>
+        <v>0.01838990300893784</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.09905493259429932</v>
+        <v>0.006458472460508347</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0237128846347332</v>
+        <v>0.009924535639584064</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.07891146093606949</v>
+        <v>0.01283564977347851</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.02139222249388695</v>
+        <v>0.008005724288523197</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.1267604976892471</v>
+        <v>0.005509273149073124</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0003127381205558777</v>
+        <v>0.007269523106515408</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.003388166427612305</v>
+        <v>0.002877536229789257</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.08257656544446945</v>
+        <v>0.02008397877216339</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.1095970124006271</v>
+        <v>0.01221092045307159</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.2037856876850128</v>
+        <v>0.01034283358603716</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.01812133193016052</v>
+        <v>0.02613498270511627</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.08512111753225327</v>
+        <v>0.01749495789408684</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.1042393371462822</v>
+        <v>0.02556805685162544</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.3277241289615631</v>
+        <v>0.002874217694625258</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.08784088492393494</v>
+        <v>0.01160664670169353</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02041900530457497</v>
+        <v>0.003472251817584038</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.1681897044181824</v>
+        <v>0.06550109386444092</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.008897252380847931</v>
+        <v>0.02235920168459415</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.02111900225281715</v>
+        <v>0.007138133980333805</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.03910678252577782</v>
+        <v>0.0009728781878948212</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.1653934866189957</v>
+        <v>0.02401137910783291</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.01421750243753195</v>
+        <v>0.009398589842021465</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.1542585492134094</v>
+        <v>0.003717087209224701</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.005293335765600204</v>
+        <v>0.0007943449891172349</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.06334363669157028</v>
+        <v>0.007542095147073269</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.1549602746963501</v>
+        <v>0.0636594146490097</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.1006045490503311</v>
+        <v>0.009589985013008118</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.07465407997369766</v>
+        <v>0.03416450321674347</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.02614344842731953</v>
+        <v>0.01395835261791945</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.2018061578273773</v>
+        <v>0.02691812440752983</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.001492686569690704</v>
+        <v>0.004855368286371231</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.293082982301712</v>
+        <v>0.01993744075298309</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.1193142682313919</v>
+        <v>0.01059003639966249</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1898107379674911</v>
+        <v>0.0203115101903677</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.08811286091804504</v>
+        <v>0.107732355594635</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.1203702166676521</v>
+        <v>0.0639999657869339</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.05026275664567947</v>
+        <v>0.02095472253859043</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.2770078182220459</v>
+        <v>0.004081865306943655</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.09206677228212357</v>
+        <v>0.02848619222640991</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.08213858306407928</v>
+        <v>0.03538958728313446</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.07433199882507324</v>
+        <v>0.02873033285140991</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.1806746274232864</v>
+        <v>0.002440757118165493</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.06133962795138359</v>
+        <v>0.03539012745022774</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.06699804216623306</v>
+        <v>0.04851552098989487</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1896710991859436</v>
+        <v>0.06218302249908447</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.1569733917713165</v>
+        <v>0.002899743150919676</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.54273921251297</v>
+        <v>0.03505216538906097</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.03919518738985062</v>
+        <v>0.01958522200584412</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.095664381980896</v>
+        <v>0.01910260692238808</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.4225878715515137</v>
+        <v>0.002314828336238861</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.103757843375206</v>
+        <v>0.004325367044657469</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.003929875791072845</v>
+        <v>0.001286847982555628</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01722720824182034</v>
+        <v>0.02127072960138321</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007324353791773319</v>
+        <v>0.00307599431835115</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008828985504806042</v>
+        <v>0.003569595515727997</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008526002638973296</v>
+        <v>0.01169901713728905</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01981794089078903</v>
+        <v>0.02390902303159237</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002456496236845851</v>
+        <v>0.000957164797000587</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007804605178534985</v>
+        <v>0.004055246710777283</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004015888087451458</v>
+        <v>0.005182140506803989</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004718213342130184</v>
+        <v>0.001034184591844678</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01272407919168472</v>
+        <v>0.03239746764302254</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002834093756973743</v>
+        <v>0.006179496645927429</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007259165868163109</v>
+        <v>0.006076482124626637</v>
       </c>
       <c r="N4" t="n">
-        <v>3.954116255044937e-05</v>
+        <v>0.004129385575652122</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01533403247594833</v>
+        <v>0.03683688119053841</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0009457534179091454</v>
+        <v>0.002174846362322569</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00669132499024272</v>
+        <v>0.005414322484284639</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001978261861950159</v>
+        <v>0.008702805265784264</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004076628829352558</v>
+        <v>0.0005684169009327888</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0002106784377247095</v>
+        <v>0.006255360785871744</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0004464591620489955</v>
+        <v>0.001815184252336621</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0007806006469763815</v>
+        <v>0.0127724027261138</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002866658614948392</v>
+        <v>0.007059889379888773</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001799632562324405</v>
+        <v>0.0045584412291646</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001274657086469233</v>
+        <v>0.0009907461935654283</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0006328998133540154</v>
+        <v>0.005851611960679293</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0002138889394700527</v>
+        <v>0.0002448594896122813</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.400502312928438e-05</v>
+        <v>0.007515962701290846</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004972053691744804</v>
+        <v>0.002903097774833441</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.002814106643199921</v>
+        <v>0.002038290491327643</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.002487964928150177</v>
+        <v>0.01084684021770954</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0006265806732699275</v>
+        <v>0.01185202784836292</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0005118510453030467</v>
+        <v>0.003682781010866165</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0005089860642328858</v>
+        <v>0.008647596463561058</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001887151505798101</v>
+        <v>0.01242519915103912</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.001508369809016585</v>
+        <v>0.008009557612240314</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.00126783805899322</v>
+        <v>0.000264269532635808</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.002089905086904764</v>
+        <v>0.006732336711138487</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001114445272833109</v>
+        <v>0.001957383938133717</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.000781299895606935</v>
+        <v>0.002047838177531958</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.005776675418019295</v>
+        <v>0.007974302396178246</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.004077791702002287</v>
+        <v>0.009110507555305958</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0008388706482946873</v>
+        <v>0.001886791200377047</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.001192207913845778</v>
+        <v>0.01332460157573223</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001112453988753259</v>
+        <v>0.004164391197264194</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.001553203794173896</v>
+        <v>0.004554920364171267</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.007439527194947004</v>
+        <v>0.04362204298377037</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002188014099374413</v>
+        <v>0.003188006579875946</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.00441015837714076</v>
+        <v>0.004840460605919361</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.002573766279965639</v>
+        <v>0.01395304687321186</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.01648629456758499</v>
+        <v>0.03095537424087524</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.002722383942455053</v>
+        <v>0.003887844504788518</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.001412902725860476</v>
+        <v>0.00512619037181139</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.003746208967640996</v>
+        <v>0.00311763072386384</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001012876280583441</v>
+        <v>0.005198728293180466</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.003004999132826924</v>
+        <v>0.01629053428769112</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0009968189988285303</v>
+        <v>0.0001469453563913703</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.003520697355270386</v>
+        <v>0.008135166950523853</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004216110333800316</v>
+        <v>0.009438196197152138</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0008828100981190801</v>
+        <v>0.006162038072943687</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.666828317567706e-05</v>
+        <v>0.01106713246554136</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001596617512404919</v>
+        <v>0.001953944796696305</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.001262650592252612</v>
+        <v>0.01001309975981712</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.002262689638882875</v>
+        <v>0.005937308538705111</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.004019191488623619</v>
+        <v>0.008467076346278191</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.001925424207001925</v>
+        <v>0.00283149816095829</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0005099761765450239</v>
+        <v>0.002694536000490189</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001828121254220605</v>
+        <v>0.001183343585580587</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.002371042035520077</v>
+        <v>0.0002097117830999196</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.000377075222786516</v>
+        <v>0.0123418690636754</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.00174680189229548</v>
+        <v>0.00269750040024519</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001480755163356662</v>
+        <v>0.003687987104058266</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.001779473037458956</v>
+        <v>0.002382583217695355</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.006412951275706291</v>
+        <v>0.02169147133827209</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001890910789370537</v>
+        <v>0.0004084964748471975</v>
       </c>
       <c r="BX4" t="n">
-        <v>7.375498535111547e-05</v>
+        <v>0.004673810675740242</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.004034760873764753</v>
+        <v>0.002601670566946268</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.008467105217278004</v>
+        <v>0.01987846195697784</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.776648948900402e-05</v>
+        <v>0.006297960877418518</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001098163658753037</v>
+        <v>0.007654979359358549</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001369550591334701</v>
+        <v>0.005772758275270462</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0004653703654184937</v>
+        <v>0.005222924053668976</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.00353160547092557</v>
+        <v>0.009575895965099335</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.727655762806535e-05</v>
+        <v>0.0004781497118528932</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.001825960353016853</v>
+        <v>0.003155572572723031</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0006321768742054701</v>
+        <v>0.005374263506382704</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002951247151941061</v>
+        <v>0.009748183190822601</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.001034134533256292</v>
+        <v>0.00528642488643527</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001590835629031062</v>
+        <v>0.001104176859371364</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0003921487659681588</v>
+        <v>0.001560441101901233</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.00312249711714685</v>
+        <v>0.01550424844026566</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0005859631346538663</v>
+        <v>0.02001464366912842</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0005995233659632504</v>
+        <v>0.0008742817444726825</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.002098148688673973</v>
+        <v>0.01714974641799927</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.006265664007514715</v>
+        <v>0.0006440049037337303</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0009328103624284267</v>
+        <v>0.0136413648724556</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.000810486963018775</v>
+        <v>0.005408952012658119</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.002507514320313931</v>
+        <v>0.008452645502984524</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0001043951197061688</v>
+        <v>0.002091201720759273</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0003980986366514117</v>
+        <v>0.006819310132414103</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.002890698378905654</v>
+        <v>0.01027722656726837</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.001031976658850908</v>
+        <v>0.0002779742644634098</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.002316384110599756</v>
+        <v>0.00106072670314461</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0003271089517511427</v>
+        <v>0.006087237969040871</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.004011604469269514</v>
+        <v>0.008965218439698219</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0002800380170810968</v>
+        <v>0.001620776485651731</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.002374887466430664</v>
+        <v>0.0004847212985623628</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0009215351892635226</v>
+        <v>5.10489335283637e-05</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.003453994868323207</v>
+        <v>0.007576391566544771</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.005982439499348402</v>
+        <v>0.001924139447510242</v>
       </c>
       <c r="DG4" t="n">
-        <v>5.524017615243793e-05</v>
+        <v>0.005175369791686535</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.003807008033618331</v>
+        <v>0.005147975869476795</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.003987825009971857</v>
+        <v>0.001964159077033401</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.002111012348905206</v>
+        <v>0.002266013994812965</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0009391585481353104</v>
+        <v>0.01017626747488976</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.009284846484661102</v>
+        <v>0.002750582527369261</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.00167902244720608</v>
+        <v>0.01159534975886345</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.001203481806442142</v>
+        <v>0.006437304895371199</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0006209448911249638</v>
+        <v>0.0086308429017663</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.001475904835388064</v>
+        <v>0.0008854779880493879</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.001886257668957114</v>
+        <v>0.01107820961624384</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.001792428316548467</v>
+        <v>0.004453902598470449</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.002306216163560748</v>
+        <v>0.007809335831552744</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.001399575034156442</v>
+        <v>0.001100512337870896</v>
       </c>
       <c r="DU4" t="n">
-        <v>6.594147998839617e-05</v>
+        <v>0.0001935363980010152</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0007844911306165159</v>
+        <v>0.003072889987379313</v>
       </c>
       <c r="DW4" t="n">
-        <v>7.869046385167167e-05</v>
+        <v>0.001074782339856029</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001022441778331995</v>
+        <v>0.002707984764128923</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.001011874061077833</v>
+        <v>0.0004215449735056609</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.001916389679536223</v>
+        <v>0.007197685539722443</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002180783310905099</v>
+        <v>0.006872755475342274</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.002551080659031868</v>
+        <v>0.009338925592601299</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.521629747003317e-05</v>
+        <v>0.0006688295397907495</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.000582246866542846</v>
+        <v>0.001649098237976432</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.001267229090444744</v>
+        <v>0.002345049288123846</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0007272785296663642</v>
+        <v>0.004781534429639578</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001226067310199142</v>
+        <v>2.712593413889408e-05</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.00197529187425971</v>
+        <v>0.0003843997837975621</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0004066958208568394</v>
+        <v>0.001308831269852817</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001918994123116136</v>
+        <v>0.009269812144339085</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001398455933667719</v>
+        <v>0.0008278578752651811</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.001216421951539814</v>
+        <v>0.0006433196249417961</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0004756950365845114</v>
+        <v>0.001664826879277825</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0007375584682449698</v>
+        <v>0.004616735968738794</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0002130158245563507</v>
+        <v>0.00455860048532486</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.003808094654232264</v>
+        <v>0.008043289184570312</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.003226150525733829</v>
+        <v>0.001874837442301214</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.002601483138278127</v>
+        <v>0.004086359404027462</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.002916863653808832</v>
+        <v>0.008896120823919773</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.00167048629373312</v>
+        <v>0.003882757853716612</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001523928949609399</v>
+        <v>0.007898155599832535</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.002932274248450994</v>
+        <v>0.001695008017122746</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.002416942268610001</v>
+        <v>0.00235859677195549</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.839421020122245e-05</v>
+        <v>0.006818409077823162</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.002838533138856292</v>
+        <v>0.01050423085689545</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0002032662741839886</v>
+        <v>7.803969492670149e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.002525130519643426</v>
+        <v>0.001306636491790414</v>
       </c>
       <c r="FB4" t="n">
-        <v>5.089605474495329e-05</v>
+        <v>0.006221532821655273</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.003369959071278572</v>
+        <v>0.008560962975025177</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0008818426867946982</v>
+        <v>0.006109615787863731</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.001719970721751451</v>
+        <v>0.002094766590744257</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0004649448965210468</v>
+        <v>0.000470240949653089</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.000232299164053984</v>
+        <v>0.0006744243437424302</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0004375985881779343</v>
+        <v>0.005705930292606354</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.001247305539436638</v>
+        <v>0.001313749002292752</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.006074155680835247</v>
+        <v>0.007512853480875492</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0009109097300097346</v>
+        <v>0.002335013821721077</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.002844062633812428</v>
+        <v>0.000559990992769599</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.001301441690884531</v>
+        <v>0.005027563311159611</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.001796774799004197</v>
+        <v>0.006491218693554401</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0002026278234552592</v>
+        <v>0.001495122211053967</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.003384814597666264</v>
+        <v>0.002939773490652442</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001452253200113773</v>
+        <v>0.007507132366299629</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.00239762756973505</v>
+        <v>0.002757348120212555</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.003633505431935191</v>
+        <v>0.0032250399235636</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.005603360943496227</v>
+        <v>0.00962481927126646</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.002629977650940418</v>
+        <v>0.01046267803758383</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0001877789036370814</v>
+        <v>0.01372712105512619</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.002846646122634411</v>
+        <v>0.005682960618287325</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0004963035462424159</v>
+        <v>0.002322719898074865</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.001090706326067448</v>
+        <v>0.002122438978403807</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0006849330966360867</v>
+        <v>1.357256769551896e-05</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.003264118451625109</v>
+        <v>0.001898580696433783</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.002869787625968456</v>
+        <v>0.005997995845973492</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.01039574760943651</v>
+        <v>0.006737291812896729</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.002202530857175589</v>
+        <v>0.0002714876318350434</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.002221778267994523</v>
+        <v>0.003831240581348538</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.00199200096540153</v>
+        <v>0.00268533593043685</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0004134975606575608</v>
+        <v>0.006647492758929729</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001361838425509632</v>
+        <v>2.04657158064947e-06</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0106643196195364</v>
+        <v>1.084972063836176e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001254528295248747</v>
+        <v>3.618080882006325e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005656022578477859</v>
+        <v>3.329746050440008e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002176459413021803</v>
+        <v>3.400195510039339e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008275041356682777</v>
+        <v>2.055983168247622e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002144711907021701</v>
+        <v>2.003585905185901e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002766638994216919</v>
+        <v>3.685696583488607e-06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0007744202157482505</v>
+        <v>7.362393716903171e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002623410196974874</v>
+        <v>1.087030568669434e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009661531075835228</v>
+        <v>1.122971661970951e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004673752700909972</v>
+        <v>5.703473107132595e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004485262092202902</v>
+        <v>5.784429504274158e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>1.687026815488935e-05</v>
+        <v>4.224674285069341e-06</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008179597556591034</v>
+        <v>2.421058525214903e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00082922208821401</v>
+        <v>1.427017991773027e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00133428000845015</v>
+        <v>5.498575319506926e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0005664055934175849</v>
+        <v>1.736178546707379e-06</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0002129242056980729</v>
+        <v>2.170126208511647e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0009442236041650176</v>
+        <v>1.759132146617048e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0007508416892960668</v>
+        <v>8.73461658557062e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00209237146191299</v>
+        <v>3.860285232804017e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0007024758378975093</v>
+        <v>1.445586690351774e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0004338131984695792</v>
+        <v>3.120822384516941e-06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0006049360381439328</v>
+        <v>1.288583462155657e-06</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001222181133925915</v>
+        <v>3.55788165506965e-06</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0009626711253076792</v>
+        <v>1.447741738047625e-06</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.03439805470407e-05</v>
+        <v>2.274670805491041e-06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0004183519340585917</v>
+        <v>1.201195004796318e-06</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0001990422897506505</v>
+        <v>3.129714968963526e-06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0003092772385571152</v>
+        <v>4.332999196776655e-06</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0002541809226386249</v>
+        <v>3.823820861725835e-06</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.234093598322943e-05</v>
+        <v>3.339619297548779e-06</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0002930510090664029</v>
+        <v>7.940864179545315e-07</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0003623785160016268</v>
+        <v>8.088580216281116e-06</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001041897805407643</v>
+        <v>1.824217633838998e-06</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.001391750760376453</v>
+        <v>3.01336308439204e-06</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.00124379200860858</v>
+        <v>2.915137201853213e-06</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0004374646523501724</v>
+        <v>2.142898665624671e-06</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0001980360539164394</v>
+        <v>2.312270225957036e-06</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0001999002124648541</v>
+        <v>2.560424036346376e-06</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.001369167119264603</v>
+        <v>2.030568339250749e-06</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0002670926041901112</v>
+        <v>6.389311693055788e-07</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.000888258102349937</v>
+        <v>4.090827587788226e-06</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.001781320665031672</v>
+        <v>1.862638441707531e-06</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0004694266535807401</v>
+        <v>1.409533069818281e-06</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.006438353098928928</v>
+        <v>1.050975060934434e-05</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0004687793843913823</v>
+        <v>4.772193733515451e-06</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001444283640012145</v>
+        <v>8.319411790580489e-07</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.002052802592515945</v>
+        <v>2.985998435178772e-06</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.00426673237234354</v>
+        <v>1.373470058751991e-05</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.000647201610263437</v>
+        <v>1.5158088899625e-06</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0007895983289927244</v>
+        <v>2.030584028034355e-06</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.002655815333127975</v>
+        <v>4.091031087227748e-07</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.001166149158962071</v>
+        <v>4.197215730528114e-07</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.002171223051846027</v>
+        <v>1.490947397542186e-06</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.003357685869559646</v>
+        <v>2.280768285345403e-06</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0008783454541116953</v>
+        <v>2.396493982814718e-06</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.001509717549197376</v>
+        <v>3.204044787707971e-06</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.002313419710844755</v>
+        <v>1.109202230509254e-06</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0001900462084449828</v>
+        <v>3.559436208888656e-06</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.001360035035759211</v>
+        <v>2.894097633543424e-06</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0006632305448874831</v>
+        <v>1.68463282079756e-06</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0002418644144199789</v>
+        <v>5.854226401424967e-07</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.002210212871432304</v>
+        <v>4.002730747743044e-06</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.001242284546606243</v>
+        <v>7.604910479130922e-07</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.001039435504935682</v>
+        <v>2.371629079789273e-06</v>
       </c>
       <c r="BP5" t="n">
-        <v>7.911217107903212e-05</v>
+        <v>9.396923132953816e-07</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0006520016468130052</v>
+        <v>1.431225200576591e-06</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.000864656176418066</v>
+        <v>2.266476712975418e-06</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0009447832126170397</v>
+        <v>1.47211369494471e-06</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0002064050349872559</v>
+        <v>2.75597267318517e-06</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0001571586617501453</v>
+        <v>1.138968968916743e-06</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.003537500509992242</v>
+        <v>6.060202395019587e-06</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.001235536648891866</v>
+        <v>6.919797783666581e-07</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.001492345705628395</v>
+        <v>2.034305452980334e-07</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.0008966822060756385</v>
+        <v>2.212855179095641e-07</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.001826900406740606</v>
+        <v>8.71670272317715e-06</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0005416743224486709</v>
+        <v>3.595977659642813e-06</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0006860897992737591</v>
+        <v>1.50568507706339e-06</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.001385903335176408</v>
+        <v>5.212852443037264e-07</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0001138567313319072</v>
+        <v>3.797172780650726e-07</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.001765231834724545</v>
+        <v>4.053581051266519e-06</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.00117918848991394</v>
+        <v>8.389058052671317e-07</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0008787063998170197</v>
+        <v>6.467844855251315e-07</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0004446656093932688</v>
+        <v>5.771743190052803e-07</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.001132333418354392</v>
+        <v>4.90994125357247e-06</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0005318910116329789</v>
+        <v>6.991700161051995e-07</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0006269293371587992</v>
+        <v>8.523805377080862e-07</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0009518828592263162</v>
+        <v>1.962407338851335e-07</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.002188831800594926</v>
+        <v>2.025732555921422e-06</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0004644031869247556</v>
+        <v>3.688984179461841e-06</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0002385110419709235</v>
+        <v>4.332599019107874e-06</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.001448785304091871</v>
+        <v>2.249453245894983e-06</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0004126890562474728</v>
+        <v>1.155342715719598e-06</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.001509485999122262</v>
+        <v>4.499073043007229e-07</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.001974331447854638</v>
+        <v>4.050850293424446e-06</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.001453984994441271</v>
+        <v>4.379517122288235e-06</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0003108708187937737</v>
+        <v>1.634134605410509e-09</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0001487386325607076</v>
+        <v>6.729373467351252e-07</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.001639951369725168</v>
+        <v>3.826848569588037e-06</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0011876035714522</v>
+        <v>1.422867057954136e-06</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.001385576790198684</v>
+        <v>1.430916199751664e-06</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0002083133440464735</v>
+        <v>6.702100563416025e-08</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.001224398263730109</v>
+        <v>5.561219040828291e-06</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0005143784219399095</v>
+        <v>1.68367279229642e-07</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.001342467265203595</v>
+        <v>1.109230765905522e-06</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0006189816631376743</v>
+        <v>1.229240922384633e-07</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0009618762414902449</v>
+        <v>8.839902534418798e-07</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0004661837592720985</v>
+        <v>7.066280431899941e-06</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0002865552087314427</v>
+        <v>4.285897375666536e-06</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.002798949833959341</v>
+        <v>2.702526217035484e-06</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.002453880617395043</v>
+        <v>2.793724434013711e-07</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001276489114388824</v>
+        <v>3.590000460462761e-06</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0009920911397784948</v>
+        <v>5.63853859603114e-07</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.001890562009066343</v>
+        <v>5.34758373760269e-06</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.002306570298969746</v>
+        <v>4.337871814641403e-06</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0003995037404820323</v>
+        <v>1.304025317949709e-06</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.000646676286123693</v>
+        <v>4.933482159685809e-06</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0005317771574482322</v>
+        <v>7.345799986069323e-07</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0002888093295041472</v>
+        <v>1.013280325423693e-06</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0003928731894120574</v>
+        <v>1.905139583868731e-06</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0006743873236700892</v>
+        <v>3.798275201916113e-06</v>
       </c>
       <c r="DT5" t="n">
-        <v>6.227396079339087e-05</v>
+        <v>1.491529474151321e-06</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0002624704211484641</v>
+        <v>4.545418050838634e-06</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.001238542376086116</v>
+        <v>2.074905012250383e-07</v>
       </c>
       <c r="DW5" t="n">
-        <v>2.069544279947877e-05</v>
+        <v>7.827727586118272e-07</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0008579897112213075</v>
+        <v>3.033303386246189e-08</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.001335086300969124</v>
+        <v>5.571041583607439e-06</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0003045467892661691</v>
+        <v>5.887441290042261e-08</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0007349404040724039</v>
+        <v>1.583135599503294e-06</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0007109990692697465</v>
+        <v>1.916035216709133e-06</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0004269634955562651</v>
+        <v>1.94475319403864e-06</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0004889930132776499</v>
+        <v>2.081128286590683e-06</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0007405992946587503</v>
+        <v>5.354286713554757e-06</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.001067471690475941</v>
+        <v>3.291309269570775e-07</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.001798357116058469</v>
+        <v>4.332973446707911e-07</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.001414262223988771</v>
+        <v>4.10307734455273e-07</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0006022201851010323</v>
+        <v>1.67075768331415e-06</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0004329279181547463</v>
+        <v>2.197448793594958e-06</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.00123670557513833</v>
+        <v>2.033129021583591e-06</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0005706184892915189</v>
+        <v>1.649512171297829e-07</v>
       </c>
       <c r="EM5" t="n">
-        <v>1.353859443042893e-05</v>
+        <v>1.972120600157723e-07</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0002690974506549537</v>
+        <v>8.787749266048195e-07</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0001294189714826643</v>
+        <v>5.011580128666537e-08</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0009925991762429476</v>
+        <v>2.322711907254416e-06</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.001089011551812291</v>
+        <v>1.177412173092307e-06</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0008322207722812891</v>
+        <v>3.312258058940643e-06</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0006888809148222208</v>
+        <v>3.873929927067365e-06</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0007815101416781545</v>
+        <v>1.641895721604669e-07</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.001555167837068439</v>
+        <v>1.91854724107543e-07</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.003056087298318744</v>
+        <v>3.53646044004563e-07</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0001696671242825687</v>
+        <v>1.620605871721637e-06</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0003870196524076164</v>
+        <v>1.901341306620452e-07</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.001549448585137725</v>
+        <v>4.14330361309112e-06</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0009962074691429734</v>
+        <v>8.152993018484267e-07</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001074153347872198</v>
+        <v>1.386079247822636e-06</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0002961384598165751</v>
+        <v>8.369713668798795e-07</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0009365743026137352</v>
+        <v>5.344882083591074e-06</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0008816376212053001</v>
+        <v>1.294739149670932e-06</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0009156716405414045</v>
+        <v>1.19213245852734e-06</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.001011420274153352</v>
+        <v>1.016045189317083e-06</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0006247606943361461</v>
+        <v>3.538805515290733e-08</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0003667950222734362</v>
+        <v>2.500723894627299e-06</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.001161877531558275</v>
+        <v>3.47796003552503e-06</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.001567943603731692</v>
+        <v>2.296031425430556e-06</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0001209484180435538</v>
+        <v>6.260859208850889e-08</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.001766754314303398</v>
+        <v>6.937804755580146e-06</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0001539748918730766</v>
+        <v>1.027447751766886e-06</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.001375369029119611</v>
+        <v>6.018906333338236e-06</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0005193491233512759</v>
+        <v>4.814255134988343e-06</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001222069375216961</v>
+        <v>3.770516968870652e-06</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0006008771015331149</v>
+        <v>3.33115804096451e-06</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.001362321199849248</v>
+        <v>3.059076561839902e-06</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.00104407430626452</v>
+        <v>3.877772087435005e-06</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001855496666394174</v>
+        <v>1.103172166949662e-06</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0006675805198028684</v>
+        <v>4.393602466734592e-06</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0008926786249503493</v>
+        <v>3.357068180775968e-06</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0008118455880321562</v>
+        <v>9.797948223422281e-06</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.0001656275126151741</v>
+        <v>8.836625511321472e-07</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.002082752995193005</v>
+        <v>2.008793671848252e-06</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0006758284289389849</v>
+        <v>8.134800850712054e-07</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0009074007393792272</v>
+        <v>4.265197276254185e-06</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0004637769889086485</v>
+        <v>3.904392542608548e-08</v>
       </c>
       <c r="GC5" t="n">
-        <v>2.045344444923103e-05</v>
+        <v>7.471867775166174e-06</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0009518374572508037</v>
+        <v>3.466039061095216e-06</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.004179020412266254</v>
+        <v>1.556839492877771e-06</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0003179261984769255</v>
+        <v>2.284733227497782e-06</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.00107607536483556</v>
+        <v>8.546584240320954e-07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0001147457587649114</v>
+        <v>5.254971124912799e-09</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001992737874388695</v>
+        <v>2.948681476766524e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.227219662629068e-05</v>
+        <v>1.10607354386616e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000799559464212507</v>
+        <v>1.159300389019791e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008278641616925597</v>
+        <v>7.986715289121094e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001053950050845742</v>
+        <v>3.090994127319391e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.505165508016944e-05</v>
+        <v>8.857348632318462e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002813252503983676</v>
+        <v>6.790759954355963e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004611325566656888</v>
+        <v>1.430993279427639e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0001412927522324026</v>
+        <v>2.338942373114605e-10</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002197798807173967</v>
+        <v>3.634021439324897e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001405476359650493</v>
+        <v>2.005875288091374e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002688507956918329</v>
+        <v>3.048709729114307e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002966428874060512</v>
+        <v>1.594445464547789e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0008116738754324615</v>
+        <v>4.229938710409442e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.630411811172962e-06</v>
+        <v>1.75469305752074e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.721029548207298e-05</v>
+        <v>2.422261502488254e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003582530771382153</v>
+        <v>1.268235294560327e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.621720002731308e-06</v>
+        <v>8.904931236841662e-10</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0002622453612275422</v>
+        <v>9.198300787716107e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001638927788008004</v>
+        <v>2.618774530560586e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002119803975801915</v>
+        <v>5.216461040902232e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0001552283647470176</v>
+        <v>9.524830701934661e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>3.97556577809155e-05</v>
+        <v>9.558808855558709e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.623149965889752e-05</v>
+        <v>1.065517629683654e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0001136506616603583</v>
+        <v>7.315478889324822e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0002174243418266997</v>
+        <v>7.111945699023181e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.084821896161884e-05</v>
+        <v>1.225815804417607e-08</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0001557536888867617</v>
+        <v>2.366492557470679e-09</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0003725546994246542</v>
+        <v>1.215694656053756e-09</v>
       </c>
       <c r="AE6" t="n">
-        <v>8.178774442058057e-05</v>
+        <v>1.381763858887552e-08</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0001221561687998474</v>
+        <v>1.306287700231223e-08</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.000190870588994585</v>
+        <v>1.785784853325367e-08</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0001817459560697898</v>
+        <v>4.134697917379526e-09</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.561165405903012e-05</v>
+        <v>3.233087042531224e-08</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0001094649342121556</v>
+        <v>3.77334252732453e-09</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0003086382930632681</v>
+        <v>9.761523811491202e-10</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0003423391317483038</v>
+        <v>8.297135423163127e-09</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0002544525486882776</v>
+        <v>7.996829864964639e-10</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.071394308382878e-05</v>
+        <v>1.643403413353894e-09</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.288147814193508e-05</v>
+        <v>4.524686403328815e-09</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0001647414319450036</v>
+        <v>4.199928405057562e-09</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.896607374073938e-05</v>
+        <v>8.515011806764505e-09</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.815042898873799e-05</v>
+        <v>9.372582709943345e-09</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.049125345773064e-05</v>
+        <v>2.531913567693778e-09</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.000144457706483081</v>
+        <v>6.444261124727291e-09</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.001316203502938151</v>
+        <v>4.30956035302188e-08</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.0004082614905200899</v>
+        <v>6.01814509337828e-09</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0002512235078029335</v>
+        <v>3.241227286565618e-09</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.729025775101036e-05</v>
+        <v>2.422826916870235e-08</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0004840182955376804</v>
+        <v>3.145759208678101e-08</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0001629677717573941</v>
+        <v>9.082528507065035e-09</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.894184555974789e-05</v>
+        <v>1.209487621167682e-09</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0001028583064908162</v>
+        <v>3.101913614855789e-09</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.426069062901661e-05</v>
+        <v>7.688473857569988e-09</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0004068098496645689</v>
+        <v>9.362567610082806e-09</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0002741773787420243</v>
+        <v>1.267456006814882e-08</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.501012542983517e-05</v>
+        <v>1.584727193915114e-08</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0006433426751755178</v>
+        <v>8.446086496860516e-09</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0004126587009523064</v>
+        <v>1.188578124811102e-10</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0001403780916007236</v>
+        <v>3.092234024393292e-09</v>
       </c>
       <c r="BJ6" t="n">
-        <v>6.128394306870177e-05</v>
+        <v>1.315665887346995e-08</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.972046634880826e-05</v>
+        <v>1.840593277790958e-08</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.000290845287963748</v>
+        <v>9.74474945181214e-11</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0002831568708643317</v>
+        <v>1.117686299068055e-08</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.898415111005306e-05</v>
+        <v>1.743151401001342e-09</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0001106990966945887</v>
+        <v>2.930201192796744e-09</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0002392923051957041</v>
+        <v>7.261733436791928e-09</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.244488157681189e-05</v>
+        <v>2.847515778725551e-09</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0001155133213615045</v>
+        <v>1.141322236719589e-08</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.41185319586657e-05</v>
+        <v>5.088790278051647e-09</v>
       </c>
       <c r="BT6" t="n">
-        <v>3.51184826286044e-05</v>
+        <v>1.263210869240083e-08</v>
       </c>
       <c r="BU6" t="n">
-        <v>9.448756463825703e-05</v>
+        <v>2.510006646971874e-09</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0008316424791701138</v>
+        <v>2.358460982065935e-08</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0001812140981201082</v>
+        <v>5.837708094702521e-11</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0001947477285284549</v>
+        <v>1.504745217317804e-09</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.107988909003325e-05</v>
+        <v>6.330366453255465e-09</v>
       </c>
       <c r="BZ6" t="n">
-        <v>7.960444781929255e-05</v>
+        <v>2.267048770931979e-08</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.13043515739264e-05</v>
+        <v>6.287367515511733e-09</v>
       </c>
       <c r="CB6" t="n">
-        <v>2.004394445975777e-05</v>
+        <v>2.721298741903411e-09</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.057473804801702e-05</v>
+        <v>2.21829221658254e-09</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.388549107010476e-05</v>
+        <v>2.728893111481057e-09</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0003378799301572144</v>
+        <v>1.036500751894209e-08</v>
       </c>
       <c r="CF6" t="n">
-        <v>1.003506622510031e-05</v>
+        <v>2.010781763317482e-09</v>
       </c>
       <c r="CG6" t="n">
-        <v>8.230000821640715e-05</v>
+        <v>2.68484035004235e-09</v>
       </c>
       <c r="CH6" t="n">
-        <v>2.804171708703507e-05</v>
+        <v>2.7335342878132e-09</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.0002133354864781722</v>
+        <v>7.894500164695728e-09</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0001393337297486141</v>
+        <v>2.579575719696692e-10</v>
       </c>
       <c r="CK6" t="n">
-        <v>2.358392339374404e-05</v>
+        <v>3.804104586890844e-09</v>
       </c>
       <c r="CL6" t="n">
-        <v>7.257518882397562e-05</v>
+        <v>4.574208567476035e-09</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0005488384631462395</v>
+        <v>3.726551955907098e-09</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0002069904730888084</v>
+        <v>1.274741823209524e-08</v>
       </c>
       <c r="CO6" t="n">
-        <v>6.224830576684326e-05</v>
+        <v>1.136419403025002e-08</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0003048241487704217</v>
+        <v>1.854544606771924e-08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0003079967282246798</v>
+        <v>3.561311912037013e-09</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0001870063570095226</v>
+        <v>1.420573703114769e-08</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0004578241205308586</v>
+        <v>4.665166919437524e-09</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0002721179334912449</v>
+        <v>1.525020820736245e-08</v>
       </c>
       <c r="CU6" t="n">
-        <v>5.213748954702169e-05</v>
+        <v>1.422999162947747e-09</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.345443979516858e-05</v>
+        <v>3.271984905239833e-09</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0003220791695639491</v>
+        <v>9.707968651184729e-09</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.986026836675592e-05</v>
+        <v>2.934281262412242e-09</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0001540858211228624</v>
+        <v>6.075046243836368e-09</v>
       </c>
       <c r="CZ6" t="n">
-        <v>6.704118277411908e-05</v>
+        <v>4.047051138655888e-09</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.000227957745664753</v>
+        <v>1.022266893357937e-08</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0001509905705461279</v>
+        <v>1.170559649210645e-09</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.000104973471025005</v>
+        <v>4.240918727305143e-09</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.539780638879165e-05</v>
+        <v>3.965982209308549e-09</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0002274831931572407</v>
+        <v>4.662025876456255e-09</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0003121421614196151</v>
+        <v>4.37835545596954e-09</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.870359483291395e-05</v>
+        <v>7.892300146750131e-10</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.000501906790304929</v>
+        <v>3.720672214768683e-09</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0005226817447692156</v>
+        <v>1.055793674709093e-09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0002332027652300894</v>
+        <v>8.605115731086244e-09</v>
       </c>
       <c r="DK6" t="n">
-        <v>6.387662142515182e-05</v>
+        <v>2.089186823539535e-09</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0001645368174649775</v>
+        <v>1.581596364985671e-08</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0002311649004695937</v>
+        <v>3.061249476132843e-09</v>
       </c>
       <c r="DN6" t="n">
-        <v>9.034486720338464e-05</v>
+        <v>4.642330964088615e-09</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.68266415130347e-05</v>
+        <v>8.777821802752328e-10</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0001187070956802927</v>
+        <v>2.678524513299863e-09</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0001539940712973475</v>
+        <v>5.835619543148596e-09</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0001560067030368373</v>
+        <v>6.978809086177762e-09</v>
       </c>
       <c r="DS6" t="n">
-        <v>9.633526497054845e-05</v>
+        <v>2.921008768197453e-09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0001102802343666553</v>
+        <v>6.495318061183752e-09</v>
       </c>
       <c r="DU6" t="n">
-        <v>7.937577902339399e-05</v>
+        <v>1.368071078644562e-08</v>
       </c>
       <c r="DV6" t="n">
-        <v>4.677134711528197e-05</v>
+        <v>5.18601783738859e-09</v>
       </c>
       <c r="DW6" t="n">
-        <v>7.776875281706452e-05</v>
+        <v>1.932061843845645e-09</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.000162773285410367</v>
+        <v>6.817629571997941e-09</v>
       </c>
       <c r="DY6" t="n">
-        <v>5.910483378102072e-05</v>
+        <v>9.232692832483735e-09</v>
       </c>
       <c r="DZ6" t="n">
-        <v>6.557166489074007e-05</v>
+        <v>9.007696810670041e-09</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0001089892029995099</v>
+        <v>5.524311230686862e-09</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0001881782955024391</v>
+        <v>3.079603239086737e-10</v>
       </c>
       <c r="EC6" t="n">
-        <v>7.452978752553463e-05</v>
+        <v>3.190169461930736e-09</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0001863539946498349</v>
+        <v>1.19798411191141e-08</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0002595514233689755</v>
+        <v>7.846233884833964e-09</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0001999970991164446</v>
+        <v>1.564239626716812e-09</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.0004296858969610184</v>
+        <v>2.850331082271396e-09</v>
       </c>
       <c r="EH6" t="n">
-        <v>6.37420525890775e-05</v>
+        <v>4.211154980282572e-09</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0001169673632830381</v>
+        <v>2.074675986563079e-09</v>
       </c>
       <c r="EJ6" t="n">
-        <v>8.996279939310625e-05</v>
+        <v>1.902062285452644e-09</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0001756296842359006</v>
+        <v>8.472029744410747e-10</v>
       </c>
       <c r="EL6" t="n">
-        <v>4.874947626376525e-05</v>
+        <v>8.105748017239733e-11</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0001624841243028641</v>
+        <v>3.576677842787035e-11</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.000121223485621158</v>
+        <v>1.577598718327522e-09</v>
       </c>
       <c r="EO6" t="n">
-        <v>1.965510455192998e-05</v>
+        <v>3.240458346098762e-09</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.0002878775703720748</v>
+        <v>5.768656219373725e-09</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0001273889793083072</v>
+        <v>1.117106962489345e-09</v>
       </c>
       <c r="ER6" t="n">
-        <v>2.259246684843674e-05</v>
+        <v>2.002890298058446e-09</v>
       </c>
       <c r="ES6" t="n">
-        <v>4.31921289418824e-05</v>
+        <v>4.234497197330711e-10</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0001362348411930725</v>
+        <v>1.131174975910199e-08</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0002107229520333931</v>
+        <v>5.802959890388593e-09</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.0003634685999713838</v>
+        <v>4.784533658153123e-09</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0001237956894328818</v>
+        <v>1.271071359276732e-09</v>
       </c>
       <c r="EX6" t="n">
-        <v>6.902849418111145e-05</v>
+        <v>2.889724903809565e-09</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0003136974992230535</v>
+        <v>1.177180752875984e-08</v>
       </c>
       <c r="EZ6" t="n">
-        <v>6.537462468259037e-05</v>
+        <v>9.3012247903701e-10</v>
       </c>
       <c r="FA6" t="n">
-        <v>7.14795824023895e-05</v>
+        <v>6.389665685446744e-09</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0001031148203765042</v>
+        <v>1.53741130937135e-09</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0002217996516264975</v>
+        <v>7.159668857781298e-09</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0001313655229751021</v>
+        <v>1.025813808896991e-10</v>
       </c>
       <c r="FE6" t="n">
-        <v>4.17632945755031e-05</v>
+        <v>1.117774761638657e-09</v>
       </c>
       <c r="FF6" t="n">
-        <v>8.236434223363176e-05</v>
+        <v>9.400100697831704e-10</v>
       </c>
       <c r="FG6" t="n">
-        <v>2.304347799508832e-05</v>
+        <v>2.167943824460394e-09</v>
       </c>
       <c r="FH6" t="n">
-        <v>9.96455637505278e-05</v>
+        <v>9.834749015169564e-09</v>
       </c>
       <c r="FI6" t="n">
-        <v>2.876204962376505e-05</v>
+        <v>6.430386889633155e-09</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0003611567663028836</v>
+        <v>6.542599795267279e-09</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0001213771902257577</v>
+        <v>4.310201084933851e-09</v>
       </c>
       <c r="FL6" t="n">
-        <v>3.605147139751352e-05</v>
+        <v>1.735846133499308e-08</v>
       </c>
       <c r="FM6" t="n">
-        <v>6.892462988616899e-05</v>
+        <v>2.240072127790427e-09</v>
       </c>
       <c r="FN6" t="n">
-        <v>9.501137537881732e-05</v>
+        <v>5.626816790282874e-09</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0001195080840261653</v>
+        <v>1.946755112669507e-08</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0002825947012752295</v>
+        <v>2.567550616561221e-10</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.0001982742105610669</v>
+        <v>1.736759713821812e-08</v>
       </c>
       <c r="FR6" t="n">
-        <v>6.77724092383869e-05</v>
+        <v>1.573149077671587e-08</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0001205373700940982</v>
+        <v>2.497740014817396e-09</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0004858171159867197</v>
+        <v>2.64564938845524e-08</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0001103042814065702</v>
+        <v>3.36000627321198e-09</v>
       </c>
       <c r="FV6" t="n">
-        <v>4.539125075098127e-05</v>
+        <v>4.173553946884567e-09</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0003813994990196079</v>
+        <v>1.098109070341025e-08</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0001315969857387245</v>
+        <v>1.039083930010065e-09</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.0002402102691121399</v>
+        <v>1.524604664737694e-09</v>
       </c>
       <c r="FZ6" t="n">
-        <v>6.700780795654282e-05</v>
+        <v>9.8770402967574e-10</v>
       </c>
       <c r="GA6" t="n">
-        <v>4.184751742286608e-05</v>
+        <v>9.567225234263788e-09</v>
       </c>
       <c r="GB6" t="n">
-        <v>3.865869803121313e-05</v>
+        <v>5.071784769938859e-09</v>
       </c>
       <c r="GC6" t="n">
-        <v>9.763924026628956e-05</v>
+        <v>1.948775540938641e-08</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0001713573437882587</v>
+        <v>1.665457993738073e-08</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0001805985230021179</v>
+        <v>3.950614058112478e-09</v>
       </c>
       <c r="GF6" t="n">
-        <v>4.830855687032454e-05</v>
+        <v>1.223109169501413e-09</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0002937118115369231</v>
+        <v>1.918811332046744e-09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.716192049583398e-10</v>
+        <v>6.268781937990298e-09</v>
       </c>
       <c r="B7" t="n">
-        <v>3.974667539541343e-10</v>
+        <v>2.247173114255929e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.938770845255622e-11</v>
+        <v>8.622447200679062e-10</v>
       </c>
       <c r="D7" t="n">
-        <v>5.330957897342614e-10</v>
+        <v>7.251645062211765e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.848556113210776e-10</v>
+        <v>2.990438119354621e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>2.924155362293845e-11</v>
+        <v>1.926008152963732e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.168814849934364e-10</v>
+        <v>3.581481777814588e-10</v>
       </c>
       <c r="H7" t="n">
-        <v>5.450299586651219e-11</v>
+        <v>6.972189048326527e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.396419230248469e-10</v>
+        <v>3.929645053801778e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.062740811492603e-10</v>
+        <v>8.227574177510633e-10</v>
       </c>
       <c r="K7" t="n">
-        <v>2.781476160507168e-10</v>
+        <v>2.656967623693163e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>4.852943741306959e-11</v>
+        <v>4.61693083764203e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.032911755600608e-10</v>
+        <v>1.465307253312176e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.933068870587419e-10</v>
+        <v>1.184990061631197e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.789038999750915e-10</v>
+        <v>2.099960916268628e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.493792949920248e-10</v>
+        <v>1.901562018957748e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.647277730887353e-10</v>
+        <v>1.443082098262494e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.563808804672107e-10</v>
+        <v>4.104207640409641e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.858999495480852e-11</v>
+        <v>3.373783474813763e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.484122685857514e-10</v>
+        <v>8.712675025890348e-11</v>
       </c>
       <c r="U7" t="n">
-        <v>5.914090051017951e-11</v>
+        <v>2.858123515636635e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>3.384079908658189e-12</v>
+        <v>4.397660902100142e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>3.104515811092057e-10</v>
+        <v>2.201760551656662e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.495893686698224e-10</v>
+        <v>2.310920566017671e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.9336231227296e-10</v>
+        <v>2.939568144455507e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.332844499854716e-11</v>
+        <v>2.321386638470813e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.276923566884136e-10</v>
+        <v>3.87794851786083e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.843884073204904e-11</v>
+        <v>8.775060678090085e-10</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.790022574610362e-10</v>
+        <v>6.568757093816657e-09</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.270188398905248e-10</v>
+        <v>8.435152576424798e-10</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.859573937172513e-11</v>
+        <v>3.365926648513096e-09</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.900682389255337e-10</v>
+        <v>7.611760111103649e-09</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.847133888181588e-11</v>
+        <v>9.672234568824933e-09</v>
       </c>
       <c r="AH7" t="n">
-        <v>9.64499521916018e-11</v>
+        <v>1.274270355899887e-09</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.310327706396166e-11</v>
+        <v>1.368639335197486e-08</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7.064147183877267e-11</v>
+        <v>1.020322715206134e-09</v>
       </c>
       <c r="AK7" t="n">
-        <v>8.821840480344179e-11</v>
+        <v>4.819664223276732e-09</v>
       </c>
       <c r="AL7" t="n">
-        <v>8.249412264405009e-11</v>
+        <v>3.866821529641129e-09</v>
       </c>
       <c r="AM7" t="n">
-        <v>4.489693339326806e-11</v>
+        <v>6.786379014300792e-09</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.028023665141433e-11</v>
+        <v>2.700789814014115e-09</v>
       </c>
       <c r="AO7" t="n">
-        <v>4.538798156761281e-12</v>
+        <v>2.293456535795713e-09</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.539532969642494e-11</v>
+        <v>2.74540923328459e-09</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.532949098885354e-11</v>
+        <v>2.426951528633481e-09</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.390357412534016e-10</v>
+        <v>1.725176113076543e-09</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.649997219554393e-11</v>
+        <v>3.22427951005011e-09</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.606173858474506e-11</v>
+        <v>6.041169342552166e-09</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.010611538372231e-10</v>
+        <v>1.943920402425192e-08</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.740311193765276e-11</v>
+        <v>7.881230779105408e-09</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.989404834785603e-10</v>
+        <v>2.01072936079072e-09</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.362151641481901e-10</v>
+        <v>2.075187310879301e-08</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.305857089128892e-10</v>
+        <v>1.811489092062857e-08</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.283583127622336e-11</v>
+        <v>3.0854581112294e-09</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.996706438025299e-11</v>
+        <v>3.185577135411677e-09</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.161077369450709e-11</v>
+        <v>2.129343590340227e-09</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.515373657256518e-11</v>
+        <v>1.994663545445974e-09</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.418888420263059e-11</v>
+        <v>3.413486160397383e-09</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.210099267103033e-11</v>
+        <v>2.112809482923694e-09</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.759414571840146e-11</v>
+        <v>7.513299316030952e-09</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.524208619902879e-10</v>
+        <v>6.551040598878899e-09</v>
       </c>
       <c r="BH7" t="n">
-        <v>1.359040241455389e-10</v>
+        <v>2.414890731827768e-09</v>
       </c>
       <c r="BI7" t="n">
-        <v>9.412933106578425e-12</v>
+        <v>5.153936832869022e-09</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.941064114996394e-10</v>
+        <v>1.033189445109883e-08</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.765943972280141e-11</v>
+        <v>7.532149348676853e-10</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.042592678857091e-10</v>
+        <v>1.445539243860594e-10</v>
       </c>
       <c r="BM7" t="n">
-        <v>4.04975358803128e-11</v>
+        <v>6.452186340766275e-09</v>
       </c>
       <c r="BN7" t="n">
-        <v>8.581566707244193e-11</v>
+        <v>1.736119026318761e-09</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.20121940172524e-10</v>
+        <v>1.227054458041721e-09</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.542180603335112e-11</v>
+        <v>7.604938900840352e-09</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.515596932151087e-11</v>
+        <v>6.916918149357798e-10</v>
       </c>
       <c r="BR7" t="n">
-        <v>9.624898100746293e-12</v>
+        <v>5.9149827258409e-09</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.639420626504574e-11</v>
+        <v>4.212158621896833e-09</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.093319681628074e-11</v>
+        <v>3.096895406784483e-09</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.136950512376945e-11</v>
+        <v>3.390156155802515e-09</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.434204558036782e-11</v>
+        <v>6.060538293439777e-09</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.239183723641631e-11</v>
+        <v>3.967266959392646e-09</v>
       </c>
       <c r="BX7" t="n">
-        <v>6.738580526910454e-11</v>
+        <v>1.619273604092086e-10</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.255170174549683e-11</v>
+        <v>2.859395831222855e-09</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.610713365606813e-11</v>
+        <v>8.983935373407803e-09</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.223176560039008e-10</v>
+        <v>5.264603419874447e-09</v>
       </c>
       <c r="CB7" t="n">
-        <v>1.214897973889073e-12</v>
+        <v>2.330947435069675e-09</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.776451373838086e-11</v>
+        <v>3.498328293716213e-10</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.502589802055866e-11</v>
+        <v>2.359346606972679e-10</v>
       </c>
       <c r="CE7" t="n">
-        <v>7.800989715311957e-11</v>
+        <v>7.216682806898689e-09</v>
       </c>
       <c r="CF7" t="n">
-        <v>7.231793636153228e-11</v>
+        <v>2.112464647652246e-10</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.514326941094325e-11</v>
+        <v>2.058283987693699e-09</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.430861245460546e-11</v>
+        <v>2.455199821227438e-09</v>
       </c>
       <c r="CI7" t="n">
-        <v>3.857057034872824e-11</v>
+        <v>4.856852697798786e-09</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.597248722173816e-11</v>
+        <v>1.60694124673455e-10</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.401626124192257e-11</v>
+        <v>2.501244544816927e-09</v>
       </c>
       <c r="CL7" t="n">
-        <v>9.284163021705538e-11</v>
+        <v>2.088857753435036e-09</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.029715479550219e-10</v>
+        <v>4.522370034010237e-09</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.847286989515752e-11</v>
+        <v>7.874750629355276e-09</v>
       </c>
       <c r="CO7" t="n">
-        <v>4.03631884859923e-11</v>
+        <v>1.254867143529736e-08</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.265528792870896e-10</v>
+        <v>8.076048274574532e-09</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.160250645559913e-10</v>
+        <v>4.299615774527865e-09</v>
       </c>
       <c r="CR7" t="n">
-        <v>7.000564017367594e-11</v>
+        <v>2.670258902881528e-09</v>
       </c>
       <c r="CS7" t="n">
-        <v>1.832725915473787e-10</v>
+        <v>1.160160967295099e-09</v>
       </c>
       <c r="CT7" t="n">
-        <v>5.800861874183383e-11</v>
+        <v>6.65402133392945e-09</v>
       </c>
       <c r="CU7" t="n">
-        <v>2.740604097828392e-11</v>
+        <v>4.955504895320928e-09</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.863376987432108e-11</v>
+        <v>1.452197362361574e-09</v>
       </c>
       <c r="CW7" t="n">
-        <v>7.294909121213777e-11</v>
+        <v>6.720001444193713e-09</v>
       </c>
       <c r="CX7" t="n">
-        <v>6.673743502272345e-11</v>
+        <v>6.344190728313492e-10</v>
       </c>
       <c r="CY7" t="n">
-        <v>7.128072437856403e-11</v>
+        <v>3.277670579393543e-09</v>
       </c>
       <c r="CZ7" t="n">
-        <v>3.621843797096957e-11</v>
+        <v>2.727856385220662e-09</v>
       </c>
       <c r="DA7" t="n">
-        <v>5.334130359635481e-11</v>
+        <v>5.831317206883568e-09</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.980383912414396e-11</v>
+        <v>9.761154107224002e-10</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.555314557699639e-11</v>
+        <v>1.959943318752266e-09</v>
       </c>
       <c r="DD7" t="n">
-        <v>8.188107136763989e-11</v>
+        <v>1.282444705985597e-09</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.135658650452953e-10</v>
+        <v>2.676230903553289e-10</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.466797378002482e-10</v>
+        <v>1.381493586194438e-09</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.384836967321945e-10</v>
+        <v>1.785675385335139e-09</v>
       </c>
       <c r="DH7" t="n">
-        <v>2.940500898329645e-10</v>
+        <v>2.408517829621815e-09</v>
       </c>
       <c r="DI7" t="n">
-        <v>4.882771964531685e-10</v>
+        <v>1.837290097839173e-09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.039115321566086e-10</v>
+        <v>9.004509138321737e-09</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.011601440976563e-10</v>
+        <v>2.262788845186492e-09</v>
       </c>
       <c r="DL7" t="n">
-        <v>3.178413088278376e-10</v>
+        <v>5.745679487745292e-09</v>
       </c>
       <c r="DM7" t="n">
-        <v>4.49838430394145e-11</v>
+        <v>2.946589194863236e-09</v>
       </c>
       <c r="DN7" t="n">
-        <v>6.493442589183829e-11</v>
+        <v>2.142732435927996e-09</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.62236282636097e-11</v>
+        <v>2.344060501258127e-09</v>
       </c>
       <c r="DP7" t="n">
-        <v>6.213531078547163e-11</v>
+        <v>1.609239963507036e-09</v>
       </c>
       <c r="DQ7" t="n">
-        <v>1.494165347004639e-10</v>
+        <v>4.47778480960892e-10</v>
       </c>
       <c r="DR7" t="n">
-        <v>3.186530900256557e-12</v>
+        <v>1.304033325766341e-09</v>
       </c>
       <c r="DS7" t="n">
-        <v>2.242020978593384e-11</v>
+        <v>3.886658772600526e-10</v>
       </c>
       <c r="DT7" t="n">
-        <v>1.131652063723898e-12</v>
+        <v>2.413466981820989e-09</v>
       </c>
       <c r="DU7" t="n">
-        <v>4.593940505781546e-11</v>
+        <v>6.187852896744062e-09</v>
       </c>
       <c r="DV7" t="n">
-        <v>1.623357698266048e-10</v>
+        <v>4.840981837617164e-09</v>
       </c>
       <c r="DW7" t="n">
-        <v>1.81563999945844e-11</v>
+        <v>2.743840932240005e-09</v>
       </c>
       <c r="DX7" t="n">
-        <v>2.267248541687472e-11</v>
+        <v>3.347888188898196e-09</v>
       </c>
       <c r="DY7" t="n">
-        <v>2.056855796794821e-10</v>
+        <v>5.63180257984186e-09</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.16876124834298e-12</v>
+        <v>3.063913345258129e-09</v>
       </c>
       <c r="EA7" t="n">
-        <v>2.394439507780177e-11</v>
+        <v>7.313501471095663e-10</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.169740082047511e-10</v>
+        <v>3.915870294690649e-09</v>
       </c>
       <c r="EC7" t="n">
-        <v>9.045635768201166e-12</v>
+        <v>1.85792714546551e-10</v>
       </c>
       <c r="ED7" t="n">
-        <v>4.577598022859064e-11</v>
+        <v>9.520403132512456e-09</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.445196740057497e-11</v>
+        <v>4.576754530916105e-09</v>
       </c>
       <c r="EF7" t="n">
-        <v>3.182811653124062e-12</v>
+        <v>2.566859613750694e-09</v>
       </c>
       <c r="EG7" t="n">
-        <v>7.656300593517074e-11</v>
+        <v>1.579193553702396e-09</v>
       </c>
       <c r="EH7" t="n">
-        <v>8.300565096375223e-11</v>
+        <v>2.530342158024723e-09</v>
       </c>
       <c r="EI7" t="n">
-        <v>7.876670149453702e-11</v>
+        <v>6.883825176551284e-10</v>
       </c>
       <c r="EJ7" t="n">
-        <v>7.301922955171847e-11</v>
+        <v>1.664984816684978e-09</v>
       </c>
       <c r="EK7" t="n">
-        <v>7.598963819299698e-11</v>
+        <v>3.467715448124409e-09</v>
       </c>
       <c r="EL7" t="n">
-        <v>3.676004639574515e-11</v>
+        <v>2.14759454664204e-09</v>
       </c>
       <c r="EM7" t="n">
-        <v>2.105410637498473e-11</v>
+        <v>4.539189857322157e-10</v>
       </c>
       <c r="EN7" t="n">
-        <v>7.617666913928289e-11</v>
+        <v>1.385310199886192e-10</v>
       </c>
       <c r="EO7" t="n">
-        <v>1.204963906431544e-11</v>
+        <v>1.029383911443915e-09</v>
       </c>
       <c r="EP7" t="n">
-        <v>4.556547500422781e-11</v>
+        <v>3.386975588881569e-09</v>
       </c>
       <c r="EQ7" t="n">
-        <v>6.572693084239134e-11</v>
+        <v>6.824274478844927e-11</v>
       </c>
       <c r="ER7" t="n">
-        <v>1.486013222196103e-11</v>
+        <v>5.685035775471192e-10</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.571447416637284e-10</v>
+        <v>9.155979308062001e-10</v>
       </c>
       <c r="ET7" t="n">
-        <v>9.904656261827682e-11</v>
+        <v>7.291486303628858e-10</v>
       </c>
       <c r="EU7" t="n">
-        <v>3.591454911244796e-11</v>
+        <v>4.031292522022056e-10</v>
       </c>
       <c r="EV7" t="n">
-        <v>2.431566059613033e-10</v>
+        <v>1.743171829104995e-09</v>
       </c>
       <c r="EW7" t="n">
-        <v>5.636589112123502e-11</v>
+        <v>2.085107642102457e-09</v>
       </c>
       <c r="EX7" t="n">
-        <v>1.950769407121911e-12</v>
+        <v>3.829335182281568e-10</v>
       </c>
       <c r="EY7" t="n">
-        <v>6.565260834978659e-11</v>
+        <v>7.832291260001512e-09</v>
       </c>
       <c r="EZ7" t="n">
-        <v>5.217728679673961e-11</v>
+        <v>3.373784862592544e-10</v>
       </c>
       <c r="FA7" t="n">
-        <v>5.048866880130731e-11</v>
+        <v>3.702685935635941e-09</v>
       </c>
       <c r="FB7" t="n">
-        <v>3.554383523618476e-11</v>
+        <v>1.071377320194244e-09</v>
       </c>
       <c r="FC7" t="n">
-        <v>3.933339418060733e-11</v>
+        <v>3.716221108618356e-09</v>
       </c>
       <c r="FD7" t="n">
-        <v>2.492323188107992e-11</v>
+        <v>2.106026741888201e-10</v>
       </c>
       <c r="FE7" t="n">
-        <v>1.429514666362319e-11</v>
+        <v>2.548569133509204e-09</v>
       </c>
       <c r="FF7" t="n">
-        <v>9.126831235217736e-11</v>
+        <v>5.067250508083987e-10</v>
       </c>
       <c r="FG7" t="n">
-        <v>1.567744892239098e-11</v>
+        <v>4.827577226862445e-11</v>
       </c>
       <c r="FH7" t="n">
-        <v>7.312486033361765e-11</v>
+        <v>5.579868123106735e-09</v>
       </c>
       <c r="FI7" t="n">
-        <v>2.273336380254065e-10</v>
+        <v>4.598130765032238e-09</v>
       </c>
       <c r="FJ7" t="n">
-        <v>2.196531012632619e-10</v>
+        <v>4.599113090364426e-09</v>
       </c>
       <c r="FK7" t="n">
-        <v>5.857365287242899e-11</v>
+        <v>3.094717371254774e-09</v>
       </c>
       <c r="FL7" t="n">
-        <v>5.461565227848908e-11</v>
+        <v>5.594599450375881e-09</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.903938985636788e-11</v>
+        <v>2.477401617184682e-09</v>
       </c>
       <c r="FN7" t="n">
-        <v>1.448881986609862e-10</v>
+        <v>3.228688427725501e-09</v>
       </c>
       <c r="FO7" t="n">
-        <v>1.024549056705126e-10</v>
+        <v>1.126156501385367e-08</v>
       </c>
       <c r="FP7" t="n">
-        <v>2.961580286564569e-11</v>
+        <v>6.00923044657975e-09</v>
       </c>
       <c r="FQ7" t="n">
-        <v>7.769096130316733e-12</v>
+        <v>1.099728041964454e-08</v>
       </c>
       <c r="FR7" t="n">
-        <v>1.503917684830824e-10</v>
+        <v>8.294386510954155e-09</v>
       </c>
       <c r="FS7" t="n">
-        <v>1.162105967011939e-10</v>
+        <v>2.180354341518864e-09</v>
       </c>
       <c r="FT7" t="n">
-        <v>2.161676809775415e-10</v>
+        <v>1.341037836333214e-09</v>
       </c>
       <c r="FU7" t="n">
-        <v>3.933279396628464e-11</v>
+        <v>4.363381878036421e-10</v>
       </c>
       <c r="FV7" t="n">
-        <v>4.106522760727316e-11</v>
+        <v>4.779711293423361e-09</v>
       </c>
       <c r="FW7" t="n">
-        <v>4.071639553293593e-11</v>
+        <v>1.031825291875066e-08</v>
       </c>
       <c r="FX7" t="n">
-        <v>1.249905734468371e-11</v>
+        <v>2.473848459416672e-09</v>
       </c>
       <c r="FY7" t="n">
-        <v>1.849008862686574e-10</v>
+        <v>1.697315399340482e-09</v>
       </c>
       <c r="FZ7" t="n">
-        <v>8.948097818262113e-11</v>
+        <v>2.048571756674278e-09</v>
       </c>
       <c r="GA7" t="n">
-        <v>3.471787440867402e-11</v>
+        <v>7.180507743953513e-09</v>
       </c>
       <c r="GB7" t="n">
-        <v>8.780149524101333e-11</v>
+        <v>1.305109131877202e-09</v>
       </c>
       <c r="GC7" t="n">
-        <v>1.880051947455996e-10</v>
+        <v>1.246911640606641e-08</v>
       </c>
       <c r="GD7" t="n">
-        <v>6.274966657393577e-11</v>
+        <v>9.527722610869205e-09</v>
       </c>
       <c r="GE7" t="n">
-        <v>2.989518632645627e-10</v>
+        <v>2.544945809646038e-09</v>
       </c>
       <c r="GF7" t="n">
-        <v>1.312299227618219e-12</v>
+        <v>1.526915927030359e-09</v>
       </c>
       <c r="GG7" t="n">
-        <v>1.18178106189859e-10</v>
+        <v>2.939986032401976e-09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0008215091074816883</v>
+        <v>2.361168299103156e-05</v>
       </c>
       <c r="B8" t="n">
-        <v>0.007357816211879253</v>
+        <v>0.0005069130565971136</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007596974610351026</v>
+        <v>0.0001795350108295679</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002901285421103239</v>
+        <v>0.0002098018449032679</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001185678644105792</v>
+        <v>1.854811853263527e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003822124563157558</v>
+        <v>0.0005148540949448943</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000451955886092037</v>
+        <v>4.986057319911197e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002513336483389139</v>
+        <v>0.0002314954035682604</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008211316308006644</v>
+        <v>0.0001216529490193352</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00168187078088522</v>
+        <v>0.0001035200548358262</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006597218103706837</v>
+        <v>0.0005949715850874782</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003580268821679056</v>
+        <v>0.0002499231486581266</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002426447346806526</v>
+        <v>0.0004454495501704514</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001952547172550112</v>
+        <v>0.0002209945232607424</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003576611168682575</v>
+        <v>0.0006037885323166847</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0003313964116387069</v>
+        <v>4.679514313465916e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0006102535990066826</v>
+        <v>7.011048728600144e-05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001637006178498268</v>
+        <v>0.0001259000127902254</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0003023514873348176</v>
+        <v>0.0001028400292852893</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0007793501717969775</v>
+        <v>4.836438165511936e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0.000668381922878325</v>
+        <v>6.479662260971963e-06</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004772191459778696</v>
+        <v>4.498981797951274e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0005813061725348234</v>
+        <v>9.0493616880849e-05</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001130633638240397</v>
+        <v>0.0001262586301891133</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0004888223484158516</v>
+        <v>0.000115302660560701</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001270859269425273</v>
+        <v>0.0001290798682020977</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001157693914137781</v>
+        <v>7.350792293436825e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0004067051340825856</v>
+        <v>6.624336674576625e-05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0004819438909180462</v>
+        <v>2.709173713810742e-05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.651000638958067e-05</v>
+        <v>9.595199662726372e-05</v>
       </c>
       <c r="AE8" t="n">
-        <v>7.823276973795146e-05</v>
+        <v>0.0001256077375728637</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0008778382325544953</v>
+        <v>0.0001428814139217138</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0003365974698681384</v>
+        <v>0.0002142470475519076</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.000314327422529459</v>
+        <v>3.422261215746403e-05</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.000212902610655874</v>
+        <v>0.0003720480599440634</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0005985636962577701</v>
+        <v>2.369873436691705e-05</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0007691995706409216</v>
+        <v>9.070755913853645e-05</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001172114629298449</v>
+        <v>6.020470027578995e-05</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0001489598944317549</v>
+        <v>5.082981078885496e-05</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0007968096761032939</v>
+        <v>8.072535274550319e-05</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0002859412925317883</v>
+        <v>0.0001110259108827449</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0009501046733930707</v>
+        <v>8.928793977247551e-05</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0005664450582116842</v>
+        <v>2.505390693841036e-05</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0001220673584612086</v>
+        <v>8.149011409841478e-05</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001031357096508145</v>
+        <v>6.865069735795259e-06</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0005972487851977348</v>
+        <v>0.0001192790296045132</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.004268782213330269</v>
+        <v>0.0004193305503576994</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0003024619072675705</v>
+        <v>0.000161472344188951</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.000675296294502914</v>
+        <v>0.0001261488650925457</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0003070602251682431</v>
+        <v>0.0004223840369377285</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.003067437093704939</v>
+        <v>0.0004671081260312349</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002042683074250817</v>
+        <v>1.783812695066445e-05</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001134681515395641</v>
+        <v>8.002384856808931e-05</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.002112460788339376</v>
+        <v>1.033380976878107e-05</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0005722347996197641</v>
+        <v>0.0001262123550986871</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.00128172873519361</v>
+        <v>2.683610728126951e-05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001583439647220075</v>
+        <v>0.0001276154507650062</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0002794331812765449</v>
+        <v>0.0001322798780165613</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0008011817699298263</v>
+        <v>0.0002016730722971261</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0005111470818519592</v>
+        <v>6.226840196177363e-05</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.000876224716193974</v>
+        <v>4.01230608986225e-05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.00128467008471489</v>
+        <v>0.0002573454694356769</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001478591118939221</v>
+        <v>6.507713987957686e-05</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0002639266895130277</v>
+        <v>2.632092946441844e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0007923795492388308</v>
+        <v>0.0001428815448889509</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0007976455963216722</v>
+        <v>5.200373561820015e-05</v>
       </c>
       <c r="BO8" t="n">
-        <v>6.533224950544536e-05</v>
+        <v>9.874247189145535e-05</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0001940045331139117</v>
+        <v>0.0001209231413668022</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0005466399015858769</v>
+        <v>7.09518208168447e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0008900591637939215</v>
+        <v>9.490567026659846e-05</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0007337903371080756</v>
+        <v>8.161296136677265e-05</v>
       </c>
       <c r="BT8" t="n">
-        <v>3.813314833678305e-05</v>
+        <v>8.107542817015201e-05</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.08155722450465e-06</v>
+        <v>7.68398167565465e-05</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.002433221088722348</v>
+        <v>0.0001625911827431992</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001224022707901895</v>
+        <v>3.023509634658694e-06</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0002091674832627177</v>
+        <v>4.858869942836463e-06</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0005235119024291635</v>
+        <v>3.40317128575407e-05</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001480267150327563</v>
+        <v>0.000246440147748217</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0003995225997641683</v>
+        <v>0.000181739596882835</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0003558454918675125</v>
+        <v>5.946312376181595e-05</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0009209542768076062</v>
+        <v>9.500309533905238e-05</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0001468190748710185</v>
+        <v>1.288792736886535e-05</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001312564476393163</v>
+        <v>0.0001655761443544179</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0006458446732722223</v>
+        <v>5.597477138508111e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0001545480045024306</v>
+        <v>4.660504782805219e-05</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0002390662557445467</v>
+        <v>4.7318622819148e-05</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0003412157238926739</v>
+        <v>0.0001290224900003523</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.000555011909455061</v>
+        <v>9.572506314725615e-06</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0005050198524259031</v>
+        <v>2.894245517381933e-05</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0006179085467010736</v>
+        <v>5.926540325162932e-07</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001559398369863629</v>
+        <v>6.446013867389411e-05</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0002937455428764224</v>
+        <v>5.944474833086133e-05</v>
       </c>
       <c r="CO8" t="n">
-        <v>3.583227953640744e-05</v>
+        <v>0.0001833692804211751</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.002599035855382681</v>
+        <v>0.000131472508655861</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0006276926142163575</v>
+        <v>8.936096855904907e-05</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0009578306926414371</v>
+        <v>5.406925993156619e-05</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.00154670502524823</v>
+        <v>0.0001602765842108056</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.001143148168921471</v>
+        <v>0.000236167325056158</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0004399843164719641</v>
+        <v>0.0001049040656653233</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0001482634979765862</v>
+        <v>5.488972965395078e-05</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.001282103592529893</v>
+        <v>0.000141042226459831</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0006782902637496591</v>
+        <v>7.862330676289275e-05</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0005645649507641792</v>
+        <v>7.207577436929569e-05</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0003633728192653507</v>
+        <v>5.295799928717315e-05</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0002311684074811637</v>
+        <v>0.0001679480192251503</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0005277460440993309</v>
+        <v>2.975814277306199e-05</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0008844244293868542</v>
+        <v>3.088625817326829e-05</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0005930714542046189</v>
+        <v>9.534956916468218e-06</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0008343485533259809</v>
+        <v>1.014861663861666e-05</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0006092777475714684</v>
+        <v>0.0001996315259020776</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0004233690269757062</v>
+        <v>0.0001691967772785574</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.001156477024778724</v>
+        <v>0.0001031243882607669</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001250251661986113</v>
+        <v>2.946358472399879e-05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.003813724033534527</v>
+        <v>0.0001469608250772581</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0006673276657238603</v>
+        <v>1.592321677890141e-05</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.001813372480683029</v>
+        <v>0.0002006993163377047</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.001558636082336307</v>
+        <v>4.118921788176522e-05</v>
       </c>
       <c r="DN8" t="n">
-        <v>2.334002056159079e-05</v>
+        <v>5.153475649422035e-05</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0006259322399273515</v>
+        <v>0.0001198892714455724</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0007168910815380514</v>
+        <v>3.115959771093912e-05</v>
       </c>
       <c r="DQ8" t="n">
-        <v>4.751826782012358e-05</v>
+        <v>0.0001183942731586285</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0004305627080611885</v>
+        <v>6.550193575094454e-06</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.001276345225051045</v>
+        <v>9.324280836153775e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001376683358103037</v>
+        <v>0.000108953652670607</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.000288891838863492</v>
+        <v>0.0002086389577016234</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0001010065025184304</v>
+        <v>8.024144335649908e-05</v>
       </c>
       <c r="DW8" t="n">
-        <v>6.435421528294683e-05</v>
+        <v>9.370094630867243e-06</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0007772127282805741</v>
+        <v>5.969551421003416e-05</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.000683779246173799</v>
+        <v>0.000173809879925102</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.001013372908346355</v>
+        <v>3.559144715836737e-06</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0004152124165557325</v>
+        <v>0.0001500970683991909</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.000545650371350348</v>
+        <v>2.175756162614562e-05</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0004468656843528152</v>
+        <v>0.0001604059507371858</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0001848116371547803</v>
+        <v>0.0001592575281392783</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001598475617356598</v>
+        <v>0.0001985089620575309</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0005698305321857333</v>
+        <v>1.529207656858489e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.001432370045222342</v>
+        <v>1.874964073067531e-05</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0005487552843987942</v>
+        <v>2.974247763631865e-05</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0003158509207423776</v>
+        <v>5.237366349319927e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.000407946587074548</v>
+        <v>4.416456795297563e-05</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.001170337316580117</v>
+        <v>4.906339017907158e-05</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0009162219939753413</v>
+        <v>3.75697563868016e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0003119456523563713</v>
+        <v>2.771158688119613e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0002561459550634027</v>
+        <v>0.0001035262685036287</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0001874671434052289</v>
+        <v>5.508178946911357e-05</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0008519500261172652</v>
+        <v>0.0001177641388494521</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0009522722102701664</v>
+        <v>7.061517680995166e-05</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0003711887402459979</v>
+        <v>0.0001281744334846735</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.001207914901897311</v>
+        <v>6.693473551422358e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0005253757699392736</v>
+        <v>0.0001364735799143091</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.001730679767206311</v>
+        <v>2.924345608334988e-06</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.001975083723664284</v>
+        <v>3.99424388888292e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0003197209734935313</v>
+        <v>2.414841765130404e-05</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0003268037107773125</v>
+        <v>4.036410973640159e-05</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.001200464088469744</v>
+        <v>0.000181354145752266</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0005563810700550675</v>
+        <v>4.441983764991164e-05</v>
       </c>
       <c r="FA8" t="n">
-        <v>1.240198616869748e-05</v>
+        <v>9.121783659793437e-05</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0002984690072480589</v>
+        <v>4.217864261590876e-05</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0001476836914662272</v>
+        <v>0.0001293058594455943</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0009641296928748488</v>
+        <v>1.555617927806452e-05</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0007885682862251997</v>
+        <v>2.631771531014238e-05</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0008531216299161315</v>
+        <v>3.487666617729701e-05</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0002685680228751153</v>
+        <v>9.244085958926007e-06</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0004212309431750327</v>
+        <v>7.253210060298443e-05</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.001085583702661097</v>
+        <v>0.0001024126977426931</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.001376043073832989</v>
+        <v>0.0001129777883761562</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0004222843563184142</v>
+        <v>1.84786222234834e-05</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0004832374979741871</v>
+        <v>0.0001790795067790896</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0005190055817365646</v>
+        <v>4.13148918596562e-05</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.000526027986779809</v>
+        <v>0.000123851903481409</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0008158473065122962</v>
+        <v>0.0002751050051301718</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0008496994851157069</v>
+        <v>0.0001100521330954507</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0001778975711204112</v>
+        <v>0.0001060959839378484</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0007066731341183186</v>
+        <v>1.917616464197636e-05</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.001005546771921217</v>
+        <v>7.538063800893724e-05</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0004911533906124532</v>
+        <v>4.125521081732586e-05</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.001013282453641295</v>
+        <v>5.533142029889859e-05</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.001066962257027626</v>
+        <v>0.0001398139720549807</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.000961143639869988</v>
+        <v>0.0004502097144722939</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0006661137449555099</v>
+        <v>9.299379598814994e-06</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.001504588406533003</v>
+        <v>6.750159082002938e-05</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0005232733092270792</v>
+        <v>9.309287997893989e-05</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0005885412101633847</v>
+        <v>0.0002356324694119394</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0002604089095257223</v>
+        <v>4.595626523951069e-05</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0009951444808393717</v>
+        <v>0.0002855887578334659</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0004141477693337947</v>
+        <v>0.0001653600193094462</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.001735927420668304</v>
+        <v>5.797818448627368e-05</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0005707900272682309</v>
+        <v>5.293959839036688e-05</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0002111555077135563</v>
+        <v>1.0623922207742e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.01861057803034782</v>
+        <v>7.691685459576547e-05</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2371256947517395</v>
+        <v>0.0003072718100156635</v>
       </c>
       <c r="C9" t="n">
-        <v>0.006445686332881451</v>
+        <v>8.086328307399526e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1187348589301109</v>
+        <v>0.000139282681629993</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0323340892791748</v>
+        <v>2.964583836728707e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.203238770365715</v>
+        <v>0.0002460949181113392</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001469207927584648</v>
+        <v>7.335331611102447e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08297643065452576</v>
+        <v>5.382629024097696e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01685802266001701</v>
+        <v>2.620859049784485e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04856201261281967</v>
+        <v>6.06481044087559e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2230824679136276</v>
+        <v>0.0003722988767549396</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004515244159847498</v>
+        <v>3.619294875534251e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08597143739461899</v>
+        <v>0.0002394993061898276</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003100891131907701</v>
+        <v>0.0001041201467160136</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1893228590488434</v>
+        <v>0.0003065447090193629</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01312901824712753</v>
+        <v>1.62144388013985e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03677046671509743</v>
+        <v>5.395979678723961e-05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.005585072096437216</v>
+        <v>5.801376391900703e-05</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01078718341886997</v>
+        <v>2.669899913598783e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01615801453590393</v>
+        <v>3.404895687708631e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02153419330716133</v>
+        <v>3.690987796289846e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03197560459375381</v>
+        <v>3.376134191057645e-05</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0583316832780838</v>
+        <v>1.433596480637789e-05</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0186696108430624</v>
+        <v>4.896780956187285e-05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01893303729593754</v>
+        <v>3.684147304738872e-05</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05739665031433105</v>
+        <v>0.0001411184493917972</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03486910462379456</v>
+        <v>8.815244655124843e-06</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001438789069652557</v>
+        <v>6.378634134307504e-05</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0133759044110775</v>
+        <v>3.182239743182436e-05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.009325931780040264</v>
+        <v>2.891817348427139e-05</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.009861024096608162</v>
+        <v>7.368098886217922e-05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01389772724360228</v>
+        <v>7.501863001380116e-05</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0143308974802494</v>
+        <v>9.57558659138158e-05</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.01284622400999069</v>
+        <v>1.038577920553507e-05</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.008509773761034012</v>
+        <v>0.0002094470110023394</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0130384424701333</v>
+        <v>3.103895505773835e-05</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02094356715679169</v>
+        <v>7.265630119945854e-05</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.04187099635601044</v>
+        <v>3.806336462730542e-05</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.002297541126608849</v>
+        <v>3.82097132387571e-05</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.008399352431297302</v>
+        <v>3.109603494522162e-05</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0009102043695747852</v>
+        <v>3.698737600643653e-06</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.02807123400270939</v>
+        <v>4.573251771944342e-06</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00256158341653645</v>
+        <v>3.918401489499956e-05</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01317024976015091</v>
+        <v>0.000139212075737305</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.02483553253114223</v>
+        <v>2.128598316630814e-05</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.03235190361738205</v>
+        <v>0.0001164827408501878</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1736998409032822</v>
+        <v>0.0002425203565508127</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.005375235341489315</v>
+        <v>6.464351463364437e-05</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.04496053233742714</v>
+        <v>6.902298628119752e-05</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.01709465309977531</v>
+        <v>0.0001876322639873251</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.1077655255794525</v>
+        <v>0.0001726334303384647</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.02394679933786392</v>
+        <v>5.942084499110933e-06</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0204777829349041</v>
+        <v>8.392642484977841e-06</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.06129929423332214</v>
+        <v>4.703050944954157e-05</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0216589942574501</v>
+        <v>1.221837555931415e-05</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03791249915957451</v>
+        <v>5.933384090894833e-05</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.04754414781928062</v>
+        <v>1.650933700148016e-05</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.00249142711982131</v>
+        <v>0.0001169502138509415</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.03823554515838623</v>
+        <v>7.435803854605183e-05</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.06128839775919914</v>
+        <v>5.427400537882932e-05</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.01917595602571964</v>
+        <v>2.736876922426745e-05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.01999368704855442</v>
+        <v>8.326924580615014e-05</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.01394461281597614</v>
+        <v>5.294046422932297e-05</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0001503666862845421</v>
+        <v>1.321857234870549e-05</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0546487532556057</v>
+        <v>3.645935066742823e-05</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.00672224722802639</v>
+        <v>1.886590212052397e-06</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01508929952979088</v>
+        <v>6.962921179365367e-05</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.003939978778362274</v>
+        <v>2.317588041478302e-05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001912229578010738</v>
+        <v>1.05286089819856e-05</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01697306707501411</v>
+        <v>0.000124360216432251</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.006471746601164341</v>
+        <v>1.833459464251064e-05</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.006727925501763821</v>
+        <v>8.065887232078239e-05</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.01539248321205378</v>
+        <v>3.784135333262384e-05</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.09007550776004791</v>
+        <v>0.0001345257624052465</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01483060978353024</v>
+        <v>2.049492104561068e-05</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.03765137121081352</v>
+        <v>6.383928848663345e-05</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.02255133725702763</v>
+        <v>3.248325811000541e-06</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.04176545515656471</v>
+        <v>8.927455201046541e-05</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.01393814291805029</v>
+        <v>3.400472633074969e-05</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0002313493750989437</v>
+        <v>2.527182368794456e-05</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.04003608599305153</v>
+        <v>4.524458199739456e-05</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.001381583511829376</v>
+        <v>1.066539516614284e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.03101350367069244</v>
+        <v>9.209743438987061e-05</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.02275220118463039</v>
+        <v>3.784714863286354e-06</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01631583645939827</v>
+        <v>3.520170139381662e-05</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.005913358181715012</v>
+        <v>1.502861596236471e-05</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0315823070704937</v>
+        <v>8.074149081949145e-05</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01641953736543655</v>
+        <v>2.530566962377634e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.01131806336343288</v>
+        <v>1.880705167423002e-05</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.02083336561918259</v>
+        <v>3.772290074266493e-05</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.05034342035651207</v>
+        <v>3.250980807933956e-05</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.007730855606496334</v>
+        <v>9.80980257736519e-05</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.005318635143339634</v>
+        <v>8.703589264769107e-05</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0362873338162899</v>
+        <v>0.0001225228043040261</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001192907337099314</v>
+        <v>2.261467670905404e-06</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.006107674911618233</v>
+        <v>8.500288822688162e-05</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.04923717677593231</v>
+        <v>5.848703949595802e-06</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.04619910195469856</v>
+        <v>0.0001025323872454464</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.009500612504780293</v>
+        <v>3.769935574382544e-05</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0001195187214761972</v>
+        <v>2.348103953409009e-05</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.02730012498795986</v>
+        <v>8.889888704288751e-05</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.01881650649011135</v>
+        <v>1.058936959452694e-06</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02870979718863964</v>
+        <v>5.380349466577172e-05</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.007997095584869385</v>
+        <v>1.63135991897434e-05</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.03324554488062859</v>
+        <v>8.741121564526111e-05</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.01652374491095543</v>
+        <v>5.449879608931951e-06</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.02352634444832802</v>
+        <v>2.382257298449986e-05</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.01090287044644356</v>
+        <v>3.269608714617789e-05</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.005340783856809139</v>
+        <v>2.506393684598152e-05</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.01120668277144432</v>
+        <v>5.012480323784985e-05</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.007310524582862854</v>
+        <v>4.254374653100967e-05</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.08527781814336777</v>
+        <v>1.193059233628446e-05</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.04483778774738312</v>
+        <v>0.0001924586395034567</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.02795918844640255</v>
+        <v>8.084376895567402e-05</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.004713171161711216</v>
+        <v>5.913638233323582e-05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.03878370299935341</v>
+        <v>1.742140739224851e-06</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.02164205349981785</v>
+        <v>2.927568857558072e-06</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.004920377396047115</v>
+        <v>3.202759035048075e-05</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0031406763009727</v>
+        <v>6.178076728247106e-05</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.01693795807659626</v>
+        <v>1.819178214645945e-05</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0004337313584983349</v>
+        <v>5.311001586960629e-05</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.008421801961958408</v>
+        <v>2.330850657017436e-05</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.002283880952745676</v>
+        <v>2.551390934968367e-05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.00104664801619947</v>
+        <v>5.983177834423259e-05</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.002834649290889502</v>
+        <v>0.0001228998880833387</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.02057269774377346</v>
+        <v>4.802750481758267e-05</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0001513669267296791</v>
+        <v>3.133450445602648e-05</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0252188928425312</v>
+        <v>1.87354235094972e-05</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.01928079500794411</v>
+        <v>3.274233677075244e-05</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.008103316649794579</v>
+        <v>4.372009425424039e-05</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.00138934375718236</v>
+        <v>6.830459460616112e-05</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.01551226247102022</v>
+        <v>4.313945100875571e-05</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0007104217074811459</v>
+        <v>3.700749584822915e-05</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.004836912266910076</v>
+        <v>6.078441219870001e-05</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0101972296833992</v>
+        <v>7.395865395665169e-05</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.01348243094980717</v>
+        <v>2.134999022018746e-06</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.03572700917720795</v>
+        <v>2.157592825824395e-05</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.01130735781043768</v>
+        <v>3.755558282136917e-05</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.007187223993241787</v>
+        <v>1.986643837881275e-06</v>
       </c>
       <c r="EJ9" t="n">
-        <v>8.202483877539635e-05</v>
+        <v>1.140911626862362e-05</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.02313658222556114</v>
+        <v>2.899988248827867e-05</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.01592731103301048</v>
+        <v>1.62789237947436e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.006859187036752701</v>
+        <v>6.775162091798848e-06</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.01097701955586672</v>
+        <v>1.743659959174693e-05</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.001153502613306046</v>
+        <v>3.267017018515617e-05</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.01492869574576616</v>
+        <v>4.102702951058745e-05</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.01754457503557205</v>
+        <v>4.007309325970709e-05</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.02199815027415752</v>
+        <v>4.721219738712534e-05</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01740813255310059</v>
+        <v>4.862611240241677e-05</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.02959133125841618</v>
+        <v>6.817911344114691e-05</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.03905221074819565</v>
+        <v>2.747707912931219e-05</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.06678984314203262</v>
+        <v>4.716587864095345e-05</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.005901198834180832</v>
+        <v>4.893737786915153e-05</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.004123020451515913</v>
+        <v>2.409339685982559e-05</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.02567833662033081</v>
+        <v>0.0001116581843234599</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0155309671536088</v>
+        <v>1.008548451864044e-06</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.02027012594044209</v>
+        <v>6.7401364503894e-05</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.004942032974213362</v>
+        <v>3.361576091265306e-05</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.02759478241205215</v>
+        <v>6.965905777178705e-05</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.02859637886285782</v>
+        <v>1.932503073476255e-05</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.01527217030525208</v>
+        <v>2.0131274141022e-05</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.02188032492995262</v>
+        <v>1.615869223314803e-05</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.01078008860349655</v>
+        <v>2.069177753583062e-05</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.007210119161754847</v>
+        <v>0.0001290930085815489</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.01567903906106949</v>
+        <v>7.44444114388898e-05</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.03749755769968033</v>
+        <v>9.857016993919387e-05</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.008984709158539772</v>
+        <v>4.490958963287994e-05</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.01825453341007233</v>
+        <v>0.0001205470762215555</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0005547641776502132</v>
+        <v>1.38623763632495e-05</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.01815658807754517</v>
+        <v>7.851590635254979e-05</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.01698459312319756</v>
+        <v>6.700785888824612e-05</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.01559801958501339</v>
+        <v>1.580220487085171e-05</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.03934814780950546</v>
+        <v>3.913992986781523e-05</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.03251191973686218</v>
+        <v>0.0001950183359440416</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0003659832291305065</v>
+        <v>3.248353459639475e-05</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.004876871593296528</v>
+        <v>0.0001110694793169387</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.01117378659546375</v>
+        <v>1.0976964404108e-05</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.02655639685690403</v>
+        <v>3.012898014276288e-05</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.004022484645247459</v>
+        <v>2.379688339715358e-05</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.01491651218384504</v>
+        <v>1.347186116618104e-05</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.04654818028211594</v>
+        <v>1.862807766883634e-05</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.01586588658392429</v>
+        <v>6.941500760149211e-05</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.02829737588763237</v>
+        <v>6.398886034730822e-05</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.01245159562677145</v>
+        <v>1.255087590834592e-05</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.01304948329925537</v>
+        <v>0.0001825021317927167</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.01801168918609619</v>
+        <v>8.525674638804048e-05</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.1004845723509789</v>
+        <v>2.506627606635448e-05</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.001938051544129848</v>
+        <v>3.56614327756688e-05</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.004058975260704756</v>
+        <v>2.736289025051519e-05</v>
       </c>
     </row>
     <row r="10">
@@ -6689,1140 +6689,1140 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.000144314777571708</v>
+        <v>9.684785027275211e-07</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001869396190159023</v>
+        <v>5.619906914944295e-06</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001237125543411821</v>
+        <v>4.913781594950706e-07</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000392859656130895</v>
+        <v>1.713130131975049e-06</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0004673385119531304</v>
+        <v>2.78321499536105e-06</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0004175872600171715</v>
+        <v>8.052302291616797e-06</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000289405114017427</v>
+        <v>2.796407898131292e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0002337529003852978</v>
+        <v>5.58515966986306e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0002795870532281697</v>
+        <v>5.080403298052261e-07</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0002041987463599071</v>
+        <v>5.367971880332334e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001648076227866113</v>
+        <v>6.849195415270515e-06</v>
       </c>
       <c r="L12" t="n">
-        <v>4.456980605027638e-06</v>
+        <v>2.680597390281036e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0002343781525269151</v>
+        <v>4.080195594724501e-06</v>
       </c>
       <c r="N12" t="n">
-        <v>7.928599370643497e-05</v>
+        <v>6.673756161035271e-06</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0003300730313640088</v>
+        <v>1.065810465661343e-05</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0001585933787282556</v>
+        <v>1.781623495844542e-06</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0001919291680678725</v>
+        <v>3.687071966851363e-06</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0003656261833384633</v>
+        <v>1.2646103186853e-07</v>
       </c>
       <c r="S12" t="n">
-        <v>8.659066224936396e-05</v>
+        <v>1.97168361637523e-08</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0002210674429079518</v>
+        <v>4.724053042082232e-07</v>
       </c>
       <c r="U12" t="n">
-        <v>6.789417966501787e-05</v>
+        <v>1.110426183004165e-06</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0001651412167120725</v>
+        <v>6.557239657922764e-07</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0002051943447440863</v>
+        <v>9.018548894346168e-07</v>
       </c>
       <c r="X12" t="n">
-        <v>6.040728112566285e-05</v>
+        <v>1.340832113783108e-06</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.820397821778897e-05</v>
+        <v>8.903189154807478e-07</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0003487916255835444</v>
+        <v>2.789565314742504e-06</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0001241104037035257</v>
+        <v>7.29408384358976e-07</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.000136229646159336</v>
+        <v>1.666501248109853e-06</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0001441746426280588</v>
+        <v>1.679826482359204e-07</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.813095877878368e-05</v>
+        <v>1.801201676698838e-07</v>
       </c>
       <c r="AE12" t="n">
-        <v>9.937054710462689e-05</v>
+        <v>2.139785920007853e-06</v>
       </c>
       <c r="AF12" t="n">
-        <v>6.070603194530122e-05</v>
+        <v>1.874179702099354e-06</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.553246955969371e-05</v>
+        <v>1.961207090062089e-06</v>
       </c>
       <c r="AH12" t="n">
-        <v>5.011488974560052e-05</v>
+        <v>3.803770027843711e-07</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.951438263058662e-05</v>
+        <v>4.753524990519509e-06</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.024465306429192e-05</v>
+        <v>1.498428218837944e-06</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0003018919960595667</v>
+        <v>7.092679084053088e-07</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0001816431031329557</v>
+        <v>1.90117475540319e-07</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.401021604076959e-05</v>
+        <v>1.454897073926986e-07</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0001500809448771179</v>
+        <v>3.587396406601329e-07</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0001624881697352976</v>
+        <v>1.036801222653594e-06</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.00012848453479819</v>
+        <v>6.078618071114761e-07</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0001283932651858777</v>
+        <v>2.119687110280211e-07</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.588609666214325e-05</v>
+        <v>2.395747287664562e-06</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0001367280056001619</v>
+        <v>3.810362727563188e-07</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.662845119833946e-05</v>
+        <v>1.187052134810074e-06</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.001121829729527235</v>
+        <v>7.045618986012414e-06</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0001618846436031163</v>
+        <v>9.731909358379198e-07</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.812497981125489e-05</v>
+        <v>9.906088962452486e-07</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.229076436487958e-05</v>
+        <v>3.979099801654229e-06</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0001172524498542771</v>
+        <v>6.843269147793762e-06</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.0004197589005343616</v>
+        <v>4.955153372065979e-07</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0001679434790275991</v>
+        <v>2.002920837185229e-06</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0001625605946173891</v>
+        <v>6.427679863918456e-07</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.578893665689975e-05</v>
+        <v>6.186841119415476e-07</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0002903149579651654</v>
+        <v>1.137914978244225e-06</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0002992796071339399</v>
+        <v>1.311314008489717e-06</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.877493721432984e-05</v>
+        <v>2.303259634572896e-06</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.000282326975138858</v>
+        <v>1.731100155666354e-06</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0002185789489885792</v>
+        <v>1.686076274154402e-07</v>
       </c>
       <c r="BI12" t="n">
-        <v>5.221756873652339e-05</v>
+        <v>7.477868848582148e-07</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0002228934463346377</v>
+        <v>4.259712113707792e-06</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0003162974899169058</v>
+        <v>4.206711423648812e-08</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0001090959849534556</v>
+        <v>7.330048390485899e-08</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0001654686639085412</v>
+        <v>2.32239881370333e-06</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.707854895968921e-05</v>
+        <v>7.285259471245809e-07</v>
       </c>
       <c r="BO12" t="n">
-        <v>8.407361747231334e-05</v>
+        <v>1.977221018023556e-06</v>
       </c>
       <c r="BP12" t="n">
-        <v>8.476828952552751e-05</v>
+        <v>1.441351173525618e-06</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.976757787109818e-05</v>
+        <v>8.206473012251081e-07</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0001225361338583753</v>
+        <v>1.970964149222709e-06</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.372489143454004e-05</v>
+        <v>1.100851250157575e-06</v>
       </c>
       <c r="BT12" t="n">
-        <v>8.294339932035655e-05</v>
+        <v>1.889286750156316e-06</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.47357417922467e-05</v>
+        <v>2.328087873593176e-07</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0006513716070912778</v>
+        <v>3.262189466113341e-06</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0001497179036960006</v>
+        <v>7.506096153520048e-07</v>
       </c>
       <c r="BX12" t="n">
-        <v>8.579660061514005e-05</v>
+        <v>1.223093363478256e-06</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.057842594804242e-05</v>
+        <v>1.550179490550363e-06</v>
       </c>
       <c r="BZ12" t="n">
-        <v>8.509851795679424e-06</v>
+        <v>3.292037717983476e-06</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.072478234069422e-05</v>
+        <v>5.93773108903406e-07</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.524679414113052e-06</v>
+        <v>1.619275508346618e-06</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.377466029836796e-05</v>
+        <v>3.921083191471553e-08</v>
       </c>
       <c r="CD12" t="n">
-        <v>8.167060877894983e-05</v>
+        <v>6.817296593908395e-08</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0003189050767105073</v>
+        <v>1.539155846330686e-06</v>
       </c>
       <c r="CF12" t="n">
-        <v>6.631863652728498e-05</v>
+        <v>3.818142886302667e-07</v>
       </c>
       <c r="CG12" t="n">
-        <v>4.623439235729165e-05</v>
+        <v>9.637009270591079e-07</v>
       </c>
       <c r="CH12" t="n">
-        <v>6.810612831031904e-05</v>
+        <v>8.825053328109789e-07</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.166157835541526e-05</v>
+        <v>2.222833472842467e-06</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.0001224772859131917</v>
+        <v>6.137962600405444e-07</v>
       </c>
       <c r="CK12" t="n">
-        <v>5.08287557750009e-05</v>
+        <v>3.518284188430698e-07</v>
       </c>
       <c r="CL12" t="n">
-        <v>8.686283399583772e-05</v>
+        <v>8.774790671850496e-07</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0004538365465123206</v>
+        <v>5.230546662460256e-08</v>
       </c>
       <c r="CN12" t="n">
-        <v>6.880261935293674e-05</v>
+        <v>3.010694854310714e-06</v>
       </c>
       <c r="CO12" t="n">
-        <v>7.271065260283649e-05</v>
+        <v>2.52499125963368e-06</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0005464509013108909</v>
+        <v>4.111414909857558e-06</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0003382407012395561</v>
+        <v>7.907331109890947e-07</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0004243392031639814</v>
+        <v>1.965241608559154e-06</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0003089748206548393</v>
+        <v>5.525971573661081e-07</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0001630076149012893</v>
+        <v>1.867475816652586e-06</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0002466056030243635</v>
+        <v>4.395261328227207e-07</v>
       </c>
       <c r="CV12" t="n">
-        <v>7.479024498024955e-05</v>
+        <v>2.268551355655291e-07</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0003035457921214402</v>
+        <v>1.296880554946256e-06</v>
       </c>
       <c r="CX12" t="n">
-        <v>6.857843982288614e-05</v>
+        <v>4.113815634809725e-07</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0001324387994827703</v>
+        <v>1.352280833089026e-06</v>
       </c>
       <c r="CZ12" t="n">
-        <v>9.321765537606552e-05</v>
+        <v>9.975418606700259e-07</v>
       </c>
       <c r="DA12" t="n">
-        <v>3.159762491122819e-05</v>
+        <v>2.628138872751151e-06</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0001223819999722764</v>
+        <v>1.381135206202089e-09</v>
       </c>
       <c r="DC12" t="n">
-        <v>9.424450399819762e-05</v>
+        <v>2.94321893079541e-07</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0001018870752886869</v>
+        <v>5.485295559992664e-07</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0001602504344191402</v>
+        <v>3.065380838052079e-07</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0002697846502996981</v>
+        <v>2.980675617436646e-06</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0001060251670423895</v>
+        <v>1.428810946890735e-06</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0002537966065574437</v>
+        <v>9.656830002313654e-08</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0005414252518676221</v>
+        <v>1.950915248016827e-06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0007134765619412065</v>
+        <v>2.240873754999484e-06</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.012119411025196e-05</v>
+        <v>8.315998911712086e-07</v>
       </c>
       <c r="DL12" t="n">
-        <v>9.285258420277387e-05</v>
+        <v>4.079189466210664e-07</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0004017963947262615</v>
+        <v>8.594325890953769e-07</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0001132622419390827</v>
+        <v>4.153641555149079e-07</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0001103864924516529</v>
+        <v>2.482081811194803e-07</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0001525800325907767</v>
+        <v>5.82933012083231e-07</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0001601546246092767</v>
+        <v>5.600585382126155e-07</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.784319313941523e-05</v>
+        <v>3.761632569876383e-07</v>
       </c>
       <c r="DS12" t="n">
-        <v>8.210854139178991e-05</v>
+        <v>1.434299576885678e-07</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0002380119840381667</v>
+        <v>1.502299028288689e-06</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0001968070573639125</v>
+        <v>2.710315811782493e-06</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0001036545509123243</v>
+        <v>4.086997762442479e-07</v>
       </c>
       <c r="DW12" t="n">
-        <v>4.389646710478701e-05</v>
+        <v>4.012409817732987e-07</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0002336534962523729</v>
+        <v>5.699266125702707e-07</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.561427289852872e-05</v>
+        <v>7.213426442831405e-07</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0002411552704870701</v>
+        <v>2.286475819346379e-06</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.000179271912202239</v>
+        <v>1.259161081179627e-06</v>
       </c>
       <c r="EB12" t="n">
-        <v>6.672294693998992e-05</v>
+        <v>1.215090833284194e-06</v>
       </c>
       <c r="EC12" t="n">
-        <v>3.868046042043716e-05</v>
+        <v>6.004449915053556e-08</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0001862592907855287</v>
+        <v>1.30082480609417e-06</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0003856640250887722</v>
+        <v>2.496816705388483e-06</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0002549297641962767</v>
+        <v>1.703787262385958e-07</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0004440037009771913</v>
+        <v>7.792694418640167e-07</v>
       </c>
       <c r="EH12" t="n">
-        <v>2.573709934949875e-05</v>
+        <v>7.194722684289445e-07</v>
       </c>
       <c r="EI12" t="n">
-        <v>1.034650631481782e-05</v>
+        <v>5.608408741863968e-07</v>
       </c>
       <c r="EJ12" t="n">
-        <v>4.685897238232428e-06</v>
+        <v>9.080452514353965e-07</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0002432379842502996</v>
+        <v>1.606322939551319e-06</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.000168841754202731</v>
+        <v>5.279367201183049e-07</v>
       </c>
       <c r="EM12" t="n">
-        <v>9.037042764248326e-05</v>
+        <v>3.415898675029894e-07</v>
       </c>
       <c r="EN12" t="n">
-        <v>2.785430297080893e-05</v>
+        <v>1.324608405184335e-07</v>
       </c>
       <c r="EO12" t="n">
-        <v>8.689709648024291e-05</v>
+        <v>4.805992261935899e-07</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0001167322843684815</v>
+        <v>2.043582526312093e-06</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0001265308383153751</v>
+        <v>1.157423412223579e-06</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0001812790287658572</v>
+        <v>6.484280561380729e-07</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0001911258441396058</v>
+        <v>2.65766459506267e-07</v>
       </c>
       <c r="ET12" t="n">
-        <v>1.449551928089932e-05</v>
+        <v>1.72747377291671e-06</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.000333867414155975</v>
+        <v>9.894220056594349e-07</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0002429642336210236</v>
+        <v>3.351842678966932e-07</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0001060033100657165</v>
+        <v>6.103690566305886e-07</v>
       </c>
       <c r="EX12" t="n">
-        <v>9.93850699160248e-05</v>
+        <v>2.63361073393753e-07</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0003124684153590351</v>
+        <v>2.125008450093446e-06</v>
       </c>
       <c r="EZ12" t="n">
-        <v>5.056027293903753e-05</v>
+        <v>1.711809005655596e-07</v>
       </c>
       <c r="FA12" t="n">
-        <v>2.398886499577202e-05</v>
+        <v>1.616353529243497e-06</v>
       </c>
       <c r="FB12" t="n">
-        <v>6.406837928807363e-05</v>
+        <v>7.178064151958097e-07</v>
       </c>
       <c r="FC12" t="n">
-        <v>9.515457350062206e-06</v>
+        <v>2.286097696924116e-06</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0001864988298621029</v>
+        <v>5.653748758049915e-07</v>
       </c>
       <c r="FE12" t="n">
-        <v>7.94623265392147e-05</v>
+        <v>1.38033925622949e-07</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0001460718340240419</v>
+        <v>1.819516910472885e-07</v>
       </c>
       <c r="FG12" t="n">
-        <v>9.368343307869509e-05</v>
+        <v>1.619992673340676e-07</v>
       </c>
       <c r="FH12" t="n">
-        <v>9.774856880540028e-05</v>
+        <v>1.995362936213496e-06</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0001715690596029162</v>
+        <v>1.335662318524555e-06</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.0002771826984826475</v>
+        <v>1.018633497551491e-06</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0001200075348606333</v>
+        <v>2.397688149358146e-06</v>
       </c>
       <c r="FL12" t="n">
-        <v>3.753237979253754e-05</v>
+        <v>2.278970214319997e-06</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0001360860042041168</v>
+        <v>1.277662249776768e-06</v>
       </c>
       <c r="FN12" t="n">
-        <v>7.71599734434858e-05</v>
+        <v>1.766970285643765e-06</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0001498602796345949</v>
+        <v>2.901727384596597e-06</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0002710186818148941</v>
+        <v>5.705722969651106e-07</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0001263443264178932</v>
+        <v>5.009051733395609e-07</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0002092294016620144</v>
+        <v>2.896080559366965e-06</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0002723265788517892</v>
+        <v>1.40922225000395e-06</v>
       </c>
       <c r="FT12" t="n">
-        <v>3.111476326012053e-05</v>
+        <v>3.967805696447613e-06</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0002428536681691185</v>
+        <v>6.030808208379312e-08</v>
       </c>
       <c r="FV12" t="n">
-        <v>7.982909301063046e-05</v>
+        <v>1.474039947879646e-07</v>
       </c>
       <c r="FW12" t="n">
-        <v>8.873403203324415e-07</v>
+        <v>4.079403879586607e-06</v>
       </c>
       <c r="FX12" t="n">
-        <v>8.96219426067546e-05</v>
+        <v>1.870885739663208e-07</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0003071661340072751</v>
+        <v>6.232333475963969e-07</v>
       </c>
       <c r="FZ12" t="n">
-        <v>8.165003237081692e-05</v>
+        <v>1.641509925320861e-06</v>
       </c>
       <c r="GA12" t="n">
-        <v>6.751508772140369e-05</v>
+        <v>2.432717565170606e-06</v>
       </c>
       <c r="GB12" t="n">
-        <v>1.665238960413262e-05</v>
+        <v>6.315553946478758e-08</v>
       </c>
       <c r="GC12" t="n">
-        <v>9.690553997643292e-05</v>
+        <v>3.058127049371251e-06</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0001629586913622916</v>
+        <v>2.686270363483345e-06</v>
       </c>
       <c r="GE12" t="n">
-        <v>1.806791988201439e-05</v>
+        <v>2.506860141693323e-07</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.0001598936360096559</v>
+        <v>6.981475735301501e-07</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0001296707923756912</v>
+        <v>7.436117925863073e-07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.00167021865490824</v>
+        <v>0.0002845706476364285</v>
       </c>
       <c r="B13" t="n">
-        <v>9.457235137233511e-05</v>
+        <v>4.116450145374984e-05</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001039326598402113</v>
+        <v>0.0003513158881105483</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0004113095346838236</v>
+        <v>4.370500391814858e-06</v>
       </c>
       <c r="E13" t="n">
-        <v>8.604559843661264e-05</v>
+        <v>0.0002429278974886984</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001741273095831275</v>
+        <v>0.0001889189588837326</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002676239528227597</v>
+        <v>0.0001904700766317546</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0008560880087316036</v>
+        <v>9.807941387407482e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>3.276838469901122e-05</v>
+        <v>5.51759876543656e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001234577037394047</v>
+        <v>0.0002218269655713812</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0001699691492831334</v>
+        <v>0.0001012149587040767</v>
       </c>
       <c r="L13" t="n">
-        <v>2.443724952172488e-05</v>
+        <v>0.000335507036652416</v>
       </c>
       <c r="M13" t="n">
-        <v>0.000219470530282706</v>
+        <v>4.957719647791237e-05</v>
       </c>
       <c r="N13" t="n">
-        <v>0.000489481317345053</v>
+        <v>0.0002134509268216789</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001377980457618833</v>
+        <v>0.0003517789882607758</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0006541566690430045</v>
+        <v>0.0001557462674099952</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.000984865939244628</v>
+        <v>7.422069029416889e-05</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0001051660001394339</v>
+        <v>6.483511242549866e-05</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0001898791088024154</v>
+        <v>9.546357614453882e-05</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0005104299052618444</v>
+        <v>0.0002309273986611515</v>
       </c>
       <c r="U13" t="n">
-        <v>3.203335654688999e-05</v>
+        <v>0.0001406455994583666</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0004628211027011275</v>
+        <v>0.0001050041464623064</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0006969345267862082</v>
+        <v>0.0001612154010217637</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0003153313009534031</v>
+        <v>0.0001811901020118967</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0003236066550016403</v>
+        <v>6.176505848998204e-05</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0001597583468537778</v>
+        <v>2.815273910528049e-05</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.049503958318383e-05</v>
+        <v>2.70626405836083e-05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003404128656256944</v>
+        <v>5.058411989011802e-05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0003432836092542857</v>
+        <v>9.519295417703688e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0001445720554329455</v>
+        <v>2.093514922307804e-06</v>
       </c>
       <c r="AE13" t="n">
-        <v>9.105939534492791e-05</v>
+        <v>4.054516466567293e-06</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.436747697880492e-05</v>
+        <v>5.25549694430083e-07</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0002059012185782194</v>
+        <v>4.096018892596476e-05</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.703036105027422e-05</v>
+        <v>8.404911932302639e-05</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0002679356839507818</v>
+        <v>2.126984327333048e-05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.354572593001649e-05</v>
+        <v>4.749907020595856e-05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0003242402744945139</v>
+        <v>1.497523044236004e-05</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.94378322805278e-05</v>
+        <v>0.0001532843452878296</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.000275331549346447</v>
+        <v>6.919736188137904e-05</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.000114569251309149</v>
+        <v>6.246727571124211e-05</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0001353005063720047</v>
+        <v>5.806615081382915e-05</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.333595668664202e-05</v>
+        <v>2.330707502551377e-05</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0001418007013853639</v>
+        <v>7.192896009655669e-05</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.619181269546971e-05</v>
+        <v>5.161129956832156e-05</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.997238905460108e-05</v>
+        <v>4.475112655200064e-05</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0009070850792340934</v>
+        <v>2.136469083779957e-05</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.000221832815441303</v>
+        <v>3.331449261168018e-05</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.402916137129068e-06</v>
+        <v>0.0001664221053943038</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0004851377452723682</v>
+        <v>7.248120527947322e-05</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.001159089268185198</v>
+        <v>7.020934572210535e-05</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0007836536387912929</v>
+        <v>0.0001953776954906061</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.000214110070373863</v>
+        <v>5.746536407968961e-05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0004195109358988702</v>
+        <v>0.0001765969209372997</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.156238719588146e-05</v>
+        <v>6.356993981171399e-05</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.000372301583411172</v>
+        <v>0.0002097870601573959</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0001624443248147145</v>
+        <v>7.369628292508423e-05</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.064738696906716e-05</v>
+        <v>4.100907972315326e-06</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.000129853084217757</v>
+        <v>2.306440728716552e-05</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0003903942997567356</v>
+        <v>6.98645890224725e-05</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0003902594035025686</v>
+        <v>9.912991663441062e-05</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0003353790671098977</v>
+        <v>7.871654815971851e-05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0004055915051139891</v>
+        <v>0.000183473268407397</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.783356805797666e-05</v>
+        <v>1.36747785290936e-05</v>
       </c>
       <c r="BL13" t="n">
-        <v>2.205625605711248e-05</v>
+        <v>0.0001067290431819856</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0002696837473195046</v>
+        <v>8.782050281297415e-05</v>
       </c>
       <c r="BN13" t="n">
-        <v>9.568194218445569e-05</v>
+        <v>0.0001613433560123667</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0004294213431421667</v>
+        <v>0.0001256528194062412</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0003837457334157079</v>
+        <v>0.0001683606387814507</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.100034857401624e-05</v>
+        <v>1.770026574376971e-05</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0003631241852417588</v>
+        <v>1.418005194864236e-05</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0004840173642151058</v>
+        <v>5.979699926683679e-05</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.000231667043408379</v>
+        <v>2.733158544288017e-05</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0004505117249209434</v>
+        <v>3.774874494411051e-05</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.000261965295067057</v>
+        <v>0.000199053916730918</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.000180715651367791</v>
+        <v>0.0001503590756328776</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0002590147196315229</v>
+        <v>7.558496145065874e-05</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0005098658730275929</v>
+        <v>0.0001156370781245641</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.000585670059081167</v>
+        <v>0.000233451573876664</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.707853804575279e-05</v>
+        <v>7.526332410634495e-06</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0001970465818885714</v>
+        <v>2.223123556177597e-05</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.544131737318821e-05</v>
+        <v>3.954645217163488e-05</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0003249882720410824</v>
+        <v>6.48438508505933e-05</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0002376708289375529</v>
+        <v>0.0001357399742119014</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.394972034380771e-05</v>
+        <v>7.506688416469842e-05</v>
       </c>
       <c r="CG13" t="n">
-        <v>1.570706444908865e-05</v>
+        <v>8.179075666703284e-05</v>
       </c>
       <c r="CH13" t="n">
-        <v>3.818058030446991e-05</v>
+        <v>5.263241473585367e-05</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0002575337130110711</v>
+        <v>5.190487354411744e-05</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.672460686881095e-05</v>
+        <v>4.671094757213723e-06</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0003021221491508186</v>
+        <v>3.474405821179971e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>3.335371002322063e-05</v>
+        <v>2.136584225809202e-05</v>
       </c>
       <c r="CM13" t="n">
-        <v>3.04564819089137e-05</v>
+        <v>2.517998109397013e-05</v>
       </c>
       <c r="CN13" t="n">
-        <v>8.544472802896053e-05</v>
+        <v>6.703023245790973e-05</v>
       </c>
       <c r="CO13" t="n">
-        <v>5.306265666149557e-05</v>
+        <v>7.228417962323874e-05</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.838301043084357e-05</v>
+        <v>4.121501842746511e-05</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0007699021953158081</v>
+        <v>6.838799163233489e-05</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0001226038439199328</v>
+        <v>3.489452501526102e-05</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0002251061087008566</v>
+        <v>0.0001264276797883213</v>
       </c>
       <c r="CT13" t="n">
-        <v>6.472003587987274e-05</v>
+        <v>4.855604493059218e-05</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0001393267011735588</v>
+        <v>1.282876110053621e-05</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0002993880480062217</v>
+        <v>6.743473204551265e-05</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0002217972651124001</v>
+        <v>9.504622721578926e-05</v>
       </c>
       <c r="CX13" t="n">
-        <v>4.503293166635558e-05</v>
+        <v>6.342241249512881e-05</v>
       </c>
       <c r="CY13" t="n">
-        <v>9.8626253020484e-05</v>
+        <v>7.703118171775714e-05</v>
       </c>
       <c r="CZ13" t="n">
-        <v>3.361049311934039e-05</v>
+        <v>4.523683310253546e-05</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0002509529876988381</v>
+        <v>5.475396028487012e-05</v>
       </c>
       <c r="DB13" t="n">
-        <v>9.168230462819338e-06</v>
+        <v>2.578637941041961e-05</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.000317820260534063</v>
+        <v>1.031508782034507e-05</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.331703944946639e-05</v>
+        <v>9.382628377352376e-06</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0001015603847918101</v>
+        <v>8.372783486265689e-05</v>
       </c>
       <c r="DF13" t="n">
-        <v>4.186153091723099e-06</v>
+        <v>2.029938332270831e-05</v>
       </c>
       <c r="DG13" t="n">
-        <v>8.462984260404482e-05</v>
+        <v>8.753647853154689e-05</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0002712910354603082</v>
+        <v>9.287933062296361e-05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001021156320348382</v>
+        <v>0.0001209652400575578</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0001048705671564676</v>
+        <v>6.690370355499908e-05</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.082425923319533e-05</v>
+        <v>3.196422039764002e-05</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0004910093848593533</v>
+        <v>3.395717430976219e-05</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0003435872786212713</v>
+        <v>1.992621764657088e-05</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0001932077575474977</v>
+        <v>3.052259125979617e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>9.108742233365774e-05</v>
+        <v>5.519985643331893e-05</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0001477284531574696</v>
+        <v>0.0001550452725496143</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0002956194803118706</v>
+        <v>0.0001169196766568348</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0002545712632127106</v>
+        <v>4.054810415254906e-05</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0002335230819880962</v>
+        <v>0.0001163043634733185</v>
       </c>
       <c r="DT13" t="n">
-        <v>1.033703301800415e-05</v>
+        <v>4.192177584627643e-05</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0004397512238938361</v>
+        <v>7.888139407441486e-06</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0001359848247375339</v>
+        <v>7.391051894956036e-06</v>
       </c>
       <c r="DW13" t="n">
-        <v>2.156382834073156e-06</v>
+        <v>4.963086030329578e-05</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.000174379616510123</v>
+        <v>4.447580795385875e-05</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.831164450384676e-06</v>
+        <v>0.0002256112347822636</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0001053648957167752</v>
+        <v>0.0001201660998049192</v>
       </c>
       <c r="EA13" t="n">
-        <v>6.966355431359261e-05</v>
+        <v>2.728130129980855e-05</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0004054703167639673</v>
+        <v>0.0001241442805621773</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0002119124983437359</v>
+        <v>2.072961251542438e-05</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.000367523287422955</v>
+        <v>2.55653740168782e-05</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0001539886288810521</v>
+        <v>1.925789547385648e-06</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0002663191989995539</v>
+        <v>3.364745498402044e-05</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0004039595078211278</v>
+        <v>0.0001899069757200778</v>
       </c>
       <c r="EH13" t="n">
-        <v>1.525594143458875e-05</v>
+        <v>1.849455293267965e-05</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0001829966640798375</v>
+        <v>5.304724982124753e-05</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0001377759617753327</v>
+        <v>0.0001031080755637959</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0001358421868644655</v>
+        <v>6.546754775627051e-06</v>
       </c>
       <c r="EL13" t="n">
-        <v>4.225572774885222e-05</v>
+        <v>2.999361277034041e-05</v>
       </c>
       <c r="EM13" t="n">
-        <v>1.93957475858042e-05</v>
+        <v>4.254993109498173e-05</v>
       </c>
       <c r="EN13" t="n">
-        <v>6.253326864680275e-05</v>
+        <v>3.496760837151669e-05</v>
       </c>
       <c r="EO13" t="n">
-        <v>9.829392365645617e-05</v>
+        <v>4.722438825410791e-05</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0003070847596973181</v>
+        <v>0.0001221645652549341</v>
       </c>
       <c r="EQ13" t="n">
-        <v>7.616166840307415e-05</v>
+        <v>6.350100011331961e-05</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.000132653716718778</v>
+        <v>1.293811146751978e-05</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0004557844949886203</v>
+        <v>3.061180905206129e-05</v>
       </c>
       <c r="ET13" t="n">
-        <v>8.481410623062402e-05</v>
+        <v>0.0001446355890948325</v>
       </c>
       <c r="EU13" t="n">
-        <v>2.369064895901829e-05</v>
+        <v>4.393735434859991e-05</v>
       </c>
       <c r="EV13" t="n">
-        <v>6.031319935573265e-05</v>
+        <v>0.0001642536517465487</v>
       </c>
       <c r="EW13" t="n">
-        <v>2.31600170081947e-05</v>
+        <v>4.494047607295215e-05</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0002573538513388485</v>
+        <v>5.405039701145142e-05</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0001832035486586392</v>
+        <v>9.381685958942398e-05</v>
       </c>
       <c r="EZ13" t="n">
-        <v>4.149982851231471e-05</v>
+        <v>5.841600795974955e-05</v>
       </c>
       <c r="FA13" t="n">
-        <v>7.206894224509597e-05</v>
+        <v>9.20398160815239e-05</v>
       </c>
       <c r="FB13" t="n">
-        <v>7.042604556772858e-05</v>
+        <v>6.559869507327676e-05</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0002192361571360379</v>
+        <v>8.444026752840728e-05</v>
       </c>
       <c r="FD13" t="n">
-        <v>5.375863838708028e-05</v>
+        <v>1.181417610496283e-05</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0004133410402573645</v>
+        <v>4.956786142429337e-06</v>
       </c>
       <c r="FF13" t="n">
-        <v>5.782567313872278e-07</v>
+        <v>3.482586180325598e-06</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0001954740146175027</v>
+        <v>0.0001010437117656693</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0002578626153990626</v>
+        <v>5.009950837120414e-05</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.000141154756420292</v>
+        <v>3.099008608842269e-05</v>
       </c>
       <c r="FJ13" t="n">
-        <v>6.83922553434968e-05</v>
+        <v>6.718456279486418e-05</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0001891303836600855</v>
+        <v>0.000169078863109462</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0002186479250667617</v>
+        <v>0.0001702331937849522</v>
       </c>
       <c r="FM13" t="n">
-        <v>5.577541378443129e-05</v>
+        <v>5.207703361520544e-05</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0001239460834767669</v>
+        <v>0.000123813355457969</v>
       </c>
       <c r="FO13" t="n">
-        <v>6.068305083317682e-06</v>
+        <v>5.254218922345899e-05</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0001530023582745343</v>
+        <v>3.392765938770026e-05</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.00013038631004747</v>
+        <v>0.0002019608800765127</v>
       </c>
       <c r="FR13" t="n">
-        <v>1.128824078477919e-05</v>
+        <v>0.0002510814229026437</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0004744056495837867</v>
+        <v>2.407183637842536e-05</v>
       </c>
       <c r="FT13" t="n">
-        <v>2.861343455151655e-05</v>
+        <v>0.0003400120476726443</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0004335285630077124</v>
+        <v>5.441458051791415e-05</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.000273186044069007</v>
+        <v>0.0002336479956284165</v>
       </c>
       <c r="FW13" t="n">
-        <v>5.068710379418917e-05</v>
+        <v>8.208354120142758e-05</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0001207228560815565</v>
+        <v>0.00012780494580511</v>
       </c>
       <c r="FY13" t="n">
-        <v>7.045459642540663e-05</v>
+        <v>3.680904046632349e-05</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0002105933090206236</v>
+        <v>5.894929927308112e-05</v>
       </c>
       <c r="GA13" t="n">
-        <v>2.326890535186976e-05</v>
+        <v>0.0001227341126650572</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0001587430451763794</v>
+        <v>4.456578244571574e-05</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0001496007316745818</v>
+        <v>3.791035123867914e-05</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0003080392198171467</v>
+        <v>5.053302811575122e-05</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0002867106813937426</v>
+        <v>4.514684769674204e-05</v>
       </c>
       <c r="GF13" t="n">
-        <v>4.808702215086669e-06</v>
+        <v>0.0002294382429681718</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0001312531239818782</v>
+        <v>6.806275632698089e-05</v>
       </c>
     </row>
   </sheetData>
